--- a/all data.xlsx
+++ b/all data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dperez/Documents/2026/Term 3/Astrophysics/GitHub/phys3116assignment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F75BEFC-518E-B74E-B4E3-1D9257E3C5EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A7826E4-2412-0E41-A24D-2406165781B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16940" xr2:uid="{75C62DBF-A087-234F-B939-43CA23AF865F}"/>
   </bookViews>
@@ -1404,7 +1404,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="47" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1414,8 +1414,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1763,9 +1761,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61345522-0AA7-6944-BB17-5F614F846001}">
   <dimension ref="A1:AO163"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="29" max="29" width="10.83203125" style="7"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
@@ -1902,7 +1897,7 @@
       <c r="AB2" t="s">
         <v>118</v>
       </c>
-      <c r="AC2" s="8"/>
+      <c r="AC2" s="4"/>
       <c r="AD2" s="4" t="s">
         <v>97</v>
       </c>
@@ -2025,7 +2020,7 @@
       <c r="AB3">
         <v>-3.1</v>
       </c>
-      <c r="AC3" s="8"/>
+      <c r="AC3" s="4"/>
       <c r="AD3" s="4">
         <v>-18</v>
       </c>
@@ -2145,7 +2140,7 @@
       <c r="AB4">
         <v>-8.9</v>
       </c>
-      <c r="AC4" s="8"/>
+      <c r="AC4" s="4"/>
       <c r="AD4" s="4">
         <v>-45.4</v>
       </c>
@@ -2268,7 +2263,7 @@
       <c r="AB5">
         <v>-6.2</v>
       </c>
-      <c r="AC5" s="8"/>
+      <c r="AC5" s="4"/>
       <c r="AD5" s="4">
         <v>223.5</v>
       </c>
@@ -2391,7 +2386,7 @@
       <c r="AB6">
         <v>-26.3</v>
       </c>
-      <c r="AC6" s="8"/>
+      <c r="AC6" s="4"/>
       <c r="AD6" s="4">
         <v>-130.6</v>
       </c>
@@ -2514,7 +2509,7 @@
       <c r="AB7">
         <v>-12.9</v>
       </c>
-      <c r="AC7" s="8"/>
+      <c r="AC7" s="4"/>
       <c r="AD7" s="4">
         <v>68.2</v>
       </c>
@@ -2637,7 +2632,7 @@
       <c r="AB8">
         <v>3.6</v>
       </c>
-      <c r="AC8" s="8"/>
+      <c r="AC8" s="4"/>
       <c r="AD8" s="4">
         <v>-82.8</v>
       </c>
@@ -2760,7 +2755,7 @@
       <c r="AB9">
         <v>-92.3</v>
       </c>
-      <c r="AC9" s="8"/>
+      <c r="AC9" s="4"/>
       <c r="AD9" s="4">
         <v>116</v>
       </c>
@@ -2883,7 +2878,7 @@
       <c r="AB10">
         <v>-59.5</v>
       </c>
-      <c r="AC10" s="8"/>
+      <c r="AC10" s="4"/>
       <c r="AD10" s="4">
         <v>-23.6</v>
       </c>
@@ -3006,7 +3001,7 @@
       <c r="AB11">
         <v>-4.3</v>
       </c>
-      <c r="AC11" s="8"/>
+      <c r="AC11" s="4"/>
       <c r="AD11" s="4">
         <v>-133</v>
       </c>
@@ -3126,7 +3121,7 @@
       <c r="AB12">
         <v>-6.9</v>
       </c>
-      <c r="AC12" s="8"/>
+      <c r="AC12" s="4"/>
       <c r="AD12" s="4">
         <v>320.5</v>
       </c>
@@ -3249,7 +3244,7 @@
       <c r="AB13">
         <v>-6.3</v>
       </c>
-      <c r="AC13" s="8"/>
+      <c r="AC13" s="4"/>
       <c r="AD13" s="4">
         <v>205.8</v>
       </c>
@@ -3372,7 +3367,7 @@
       <c r="AB14">
         <v>-3</v>
       </c>
-      <c r="AC14" s="8"/>
+      <c r="AC14" s="4"/>
       <c r="AD14" s="4">
         <v>148.9</v>
       </c>
@@ -3492,7 +3487,7 @@
       <c r="AB15">
         <v>35.200000000000003</v>
       </c>
-      <c r="AC15" s="8"/>
+      <c r="AC15" s="4"/>
       <c r="AD15" s="4">
         <v>-20.2</v>
       </c>
@@ -3615,7 +3610,7 @@
       <c r="AB16">
         <v>15</v>
       </c>
-      <c r="AC16" s="8"/>
+      <c r="AC16" s="4"/>
       <c r="AD16" s="4" t="s">
         <v>109</v>
       </c>
@@ -3738,7 +3733,7 @@
       <c r="AB17">
         <v>4.8</v>
       </c>
-      <c r="AC17" s="8"/>
+      <c r="AC17" s="4"/>
       <c r="AD17" s="4">
         <v>34.299999999999997</v>
       </c>
@@ -3861,7 +3856,7 @@
       <c r="AB18">
         <v>-1.9</v>
       </c>
-      <c r="AC18" s="8"/>
+      <c r="AC18" s="4"/>
       <c r="AD18" s="4">
         <v>101.6</v>
       </c>
@@ -3984,7 +3979,7 @@
       <c r="AB19">
         <v>-2.6</v>
       </c>
-      <c r="AC19" s="8"/>
+      <c r="AC19" s="4"/>
       <c r="AD19" s="4" t="s">
         <v>109</v>
       </c>
@@ -4104,7 +4099,7 @@
       <c r="AB20">
         <v>61.7</v>
       </c>
-      <c r="AC20" s="8"/>
+      <c r="AC20" s="4"/>
       <c r="AD20" s="4">
         <v>83.4</v>
       </c>
@@ -4224,7 +4219,7 @@
       <c r="AB21">
         <v>0.7</v>
       </c>
-      <c r="AC21" s="8"/>
+      <c r="AC21" s="4"/>
       <c r="AD21" s="4">
         <v>494</v>
       </c>
@@ -4347,7 +4342,7 @@
       <c r="AB22">
         <v>103.2</v>
       </c>
-      <c r="AC22" s="8"/>
+      <c r="AC22" s="4"/>
       <c r="AD22" s="4">
         <v>74.5</v>
       </c>
@@ -4467,7 +4462,7 @@
       <c r="AB23">
         <v>45.6</v>
       </c>
-      <c r="AC23" s="8"/>
+      <c r="AC23" s="4"/>
       <c r="AD23" s="4" t="s">
         <v>109</v>
       </c>
@@ -4587,7 +4582,7 @@
       <c r="AB24">
         <v>18.8</v>
       </c>
-      <c r="AC24" s="8"/>
+      <c r="AC24" s="4"/>
       <c r="AD24" s="4">
         <v>183.2</v>
       </c>
@@ -4707,7 +4702,7 @@
       <c r="AB25">
         <v>-1</v>
       </c>
-      <c r="AC25" s="8"/>
+      <c r="AC25" s="4"/>
       <c r="AD25" s="4">
         <v>72.3</v>
       </c>
@@ -4827,7 +4822,7 @@
       <c r="AB26">
         <v>4.3</v>
       </c>
-      <c r="AC26" s="8"/>
+      <c r="AC26" s="4"/>
       <c r="AD26" s="4">
         <v>-44</v>
       </c>
@@ -4947,7 +4942,7 @@
       <c r="AB27">
         <v>6</v>
       </c>
-      <c r="AC27" s="8"/>
+      <c r="AC27" s="4"/>
       <c r="AD27" s="4">
         <v>-94.7</v>
       </c>
@@ -5070,7 +5065,7 @@
       <c r="AB28">
         <v>-0.9</v>
       </c>
-      <c r="AC28" s="8"/>
+      <c r="AC28" s="4"/>
       <c r="AD28" s="4">
         <v>200.2</v>
       </c>
@@ -5193,7 +5188,7 @@
       <c r="AB29">
         <v>17.600000000000001</v>
       </c>
-      <c r="AC29" s="8"/>
+      <c r="AC29" s="4"/>
       <c r="AD29" s="4">
         <v>-62.9</v>
       </c>
@@ -5316,7 +5311,7 @@
       <c r="AB30">
         <v>17.100000000000001</v>
       </c>
-      <c r="AC30" s="8"/>
+      <c r="AC30" s="4"/>
       <c r="AD30" s="4">
         <v>44</v>
       </c>
@@ -5439,7 +5434,7 @@
       <c r="AB31">
         <v>1.3</v>
       </c>
-      <c r="AC31" s="8"/>
+      <c r="AC31" s="4"/>
       <c r="AD31" s="4">
         <v>232.1</v>
       </c>
@@ -5562,7 +5557,7 @@
       <c r="AB32">
         <v>10</v>
       </c>
-      <c r="AC32" s="8"/>
+      <c r="AC32" s="4"/>
       <c r="AD32" s="4">
         <v>-147.6</v>
       </c>
@@ -5685,7 +5680,7 @@
       <c r="AB33">
         <v>2.1</v>
       </c>
-      <c r="AC33" s="8"/>
+      <c r="AC33" s="4"/>
       <c r="AD33" s="4">
         <v>57.4</v>
       </c>
@@ -5808,7 +5803,7 @@
       <c r="AB34">
         <v>17.8</v>
       </c>
-      <c r="AC34" s="8"/>
+      <c r="AC34" s="4"/>
       <c r="AD34" s="4" t="s">
         <v>109</v>
       </c>
@@ -5928,7 +5923,7 @@
       <c r="AB35">
         <v>15.3</v>
       </c>
-      <c r="AC35" s="8"/>
+      <c r="AC35" s="4"/>
       <c r="AD35" s="4">
         <v>110.7</v>
       </c>
@@ -6048,7 +6043,7 @@
       <c r="AB36">
         <v>19.100000000000001</v>
       </c>
-      <c r="AC36" s="8"/>
+      <c r="AC36" s="4"/>
       <c r="AD36" s="4">
         <v>-45.1</v>
       </c>
@@ -6168,7 +6163,7 @@
       <c r="AB37">
         <v>17.7</v>
       </c>
-      <c r="AC37" s="8"/>
+      <c r="AC37" s="4"/>
       <c r="AD37" s="4">
         <v>-140.30000000000001</v>
       </c>
@@ -6291,7 +6286,7 @@
       <c r="AB38">
         <v>-6.6</v>
       </c>
-      <c r="AC38" s="8"/>
+      <c r="AC38" s="4"/>
       <c r="AD38" s="4">
         <v>31.5</v>
       </c>
@@ -6414,7 +6409,7 @@
       <c r="AB39">
         <v>12.1</v>
       </c>
-      <c r="AC39" s="8"/>
+      <c r="AC39" s="4"/>
       <c r="AD39" s="4">
         <v>-27.5</v>
       </c>
@@ -6537,7 +6532,7 @@
       <c r="AB40">
         <v>16.7</v>
       </c>
-      <c r="AC40" s="8"/>
+      <c r="AC40" s="4"/>
       <c r="AD40" s="4">
         <v>-58.7</v>
       </c>
@@ -6657,7 +6652,7 @@
       <c r="AB41">
         <v>6.3</v>
       </c>
-      <c r="AC41" s="8"/>
+      <c r="AC41" s="4"/>
       <c r="AD41" s="4">
         <v>101.5</v>
       </c>
@@ -6777,7 +6772,7 @@
       <c r="AB42">
         <v>5.5</v>
       </c>
-      <c r="AC42" s="8"/>
+      <c r="AC42" s="4"/>
       <c r="AD42" s="4">
         <v>53.2</v>
       </c>
@@ -6897,7 +6892,7 @@
       <c r="AB43">
         <v>0.7</v>
       </c>
-      <c r="AC43" s="8"/>
+      <c r="AC43" s="4"/>
       <c r="AD43" s="4">
         <v>-107.5</v>
       </c>
@@ -7017,7 +7012,7 @@
       <c r="AB44">
         <v>0.8</v>
       </c>
-      <c r="AC44" s="8"/>
+      <c r="AC44" s="4"/>
       <c r="AD44" s="4">
         <v>128.4</v>
       </c>
@@ -7140,7 +7135,7 @@
       <c r="AB45">
         <v>1.4</v>
       </c>
-      <c r="AC45" s="8"/>
+      <c r="AC45" s="4"/>
       <c r="AD45" s="4" t="s">
         <v>109</v>
       </c>
@@ -7260,7 +7255,7 @@
       <c r="AB46">
         <v>2.4</v>
       </c>
-      <c r="AC46" s="8"/>
+      <c r="AC46" s="4"/>
       <c r="AD46" s="4">
         <v>88.9</v>
       </c>
@@ -7380,7 +7375,7 @@
       <c r="AB47">
         <v>-0.4</v>
       </c>
-      <c r="AC47" s="8"/>
+      <c r="AC47" s="4"/>
       <c r="AD47" s="4">
         <v>8</v>
       </c>
@@ -7503,7 +7498,7 @@
       <c r="AB48">
         <v>51.4</v>
       </c>
-      <c r="AC48" s="8"/>
+      <c r="AC48" s="4"/>
       <c r="AD48" s="4">
         <v>72.3</v>
       </c>
@@ -7626,7 +7621,7 @@
       <c r="AB49">
         <v>3.3</v>
       </c>
-      <c r="AC49" s="8"/>
+      <c r="AC49" s="4"/>
       <c r="AD49" s="4">
         <v>8.1</v>
       </c>
@@ -7749,7 +7744,7 @@
       <c r="AB50">
         <v>0.6</v>
       </c>
-      <c r="AC50" s="8"/>
+      <c r="AC50" s="4"/>
       <c r="AD50" s="4">
         <v>70.7</v>
       </c>
@@ -7872,7 +7867,7 @@
       <c r="AB51">
         <v>-4.2</v>
       </c>
-      <c r="AC51" s="8"/>
+      <c r="AC51" s="4"/>
       <c r="AD51" s="4">
         <v>361.4</v>
       </c>
@@ -7995,7 +7990,7 @@
       <c r="AB52">
         <v>2.4</v>
       </c>
-      <c r="AC52" s="8"/>
+      <c r="AC52" s="4"/>
       <c r="AD52" s="4">
         <v>193.8</v>
       </c>
@@ -8118,7 +8113,7 @@
       <c r="AB53">
         <v>1.2</v>
       </c>
-      <c r="AC53" s="8"/>
+      <c r="AC53" s="4"/>
       <c r="AD53" s="4">
         <v>6.7</v>
       </c>
@@ -8241,7 +8236,7 @@
       <c r="AB54">
         <v>1.3</v>
       </c>
-      <c r="AC54" s="8"/>
+      <c r="AC54" s="4"/>
       <c r="AD54" s="4">
         <v>-136.30000000000001</v>
       </c>
@@ -8361,7 +8356,7 @@
       <c r="AB55">
         <v>2.5</v>
       </c>
-      <c r="AC55" s="8"/>
+      <c r="AC55" s="4"/>
       <c r="AD55" s="4">
         <v>-34.1</v>
       </c>
@@ -8481,7 +8476,7 @@
       <c r="AB56">
         <v>1.7</v>
       </c>
-      <c r="AC56" s="8"/>
+      <c r="AC56" s="4"/>
       <c r="AD56" s="4" t="s">
         <v>109</v>
       </c>
@@ -8601,7 +8596,7 @@
       <c r="AB57">
         <v>4.7</v>
       </c>
-      <c r="AC57" s="8"/>
+      <c r="AC57" s="4"/>
       <c r="AD57" s="4">
         <v>-244.2</v>
       </c>
@@ -8690,7 +8685,7 @@
       <c r="AB58">
         <v>19.7</v>
       </c>
-      <c r="AC58" s="8"/>
+      <c r="AC58" s="4"/>
       <c r="AD58" s="4">
         <v>-154.19999999999999</v>
       </c>
@@ -8779,7 +8774,7 @@
       <c r="AB59">
         <v>2.1</v>
       </c>
-      <c r="AC59" s="8"/>
+      <c r="AC59" s="4"/>
       <c r="AD59" s="4">
         <v>-41.4</v>
       </c>
@@ -8868,7 +8863,7 @@
       <c r="AB60">
         <v>-0.3</v>
       </c>
-      <c r="AC60" s="8"/>
+      <c r="AC60" s="4"/>
       <c r="AD60" s="4" t="s">
         <v>109</v>
       </c>
@@ -8957,7 +8952,7 @@
       <c r="AB61">
         <v>2.7</v>
       </c>
-      <c r="AC61" s="8"/>
+      <c r="AC61" s="4"/>
       <c r="AD61" s="4">
         <v>87.3</v>
       </c>
@@ -9046,7 +9041,7 @@
       <c r="AB62">
         <v>1.7</v>
       </c>
-      <c r="AC62" s="8"/>
+      <c r="AC62" s="4"/>
       <c r="AD62" s="4">
         <v>75.2</v>
       </c>
@@ -9135,7 +9130,7 @@
       <c r="AB63">
         <v>0.6</v>
       </c>
-      <c r="AC63" s="8"/>
+      <c r="AC63" s="4"/>
       <c r="AD63" s="4">
         <v>-101.4</v>
       </c>
@@ -9207,7 +9202,7 @@
       <c r="AB64">
         <v>18.600000000000001</v>
       </c>
-      <c r="AC64" s="8"/>
+      <c r="AC64" s="4"/>
       <c r="AD64" s="4">
         <v>68.900000000000006</v>
       </c>
@@ -9279,7 +9274,7 @@
       <c r="AB65">
         <v>0.9</v>
       </c>
-      <c r="AC65" s="8"/>
+      <c r="AC65" s="4"/>
       <c r="AD65" s="4">
         <v>-70.099999999999994</v>
       </c>
@@ -9351,7 +9346,7 @@
       <c r="AB66">
         <v>1.4</v>
       </c>
-      <c r="AC66" s="8"/>
+      <c r="AC66" s="4"/>
       <c r="AD66" s="4">
         <v>135</v>
       </c>
@@ -9423,7 +9418,7 @@
       <c r="AB67">
         <v>2.6</v>
       </c>
-      <c r="AC67" s="8"/>
+      <c r="AC67" s="4"/>
       <c r="AD67" s="4">
         <v>27.5</v>
       </c>
@@ -9495,7 +9490,7 @@
       <c r="AB68">
         <v>1.8</v>
       </c>
-      <c r="AC68" s="8"/>
+      <c r="AC68" s="4"/>
       <c r="AD68" s="4">
         <v>-288.7</v>
       </c>
@@ -9567,7 +9562,7 @@
       <c r="AB69">
         <v>1.3</v>
       </c>
-      <c r="AC69" s="8"/>
+      <c r="AC69" s="4"/>
       <c r="AD69" s="4">
         <v>-146.19999999999999</v>
       </c>
@@ -9639,7 +9634,7 @@
       <c r="AB70">
         <v>0.6</v>
       </c>
-      <c r="AC70" s="8"/>
+      <c r="AC70" s="4"/>
       <c r="AD70" s="4">
         <v>-107.3</v>
       </c>
@@ -9711,7 +9706,7 @@
       <c r="AB71">
         <v>1</v>
       </c>
-      <c r="AC71" s="8"/>
+      <c r="AC71" s="4"/>
       <c r="AD71" s="4">
         <v>71.400000000000006</v>
       </c>
@@ -9783,7 +9778,7 @@
       <c r="AB72">
         <v>4.7</v>
       </c>
-      <c r="AC72" s="8"/>
+      <c r="AC72" s="4"/>
       <c r="AD72" s="4">
         <v>-120</v>
       </c>
@@ -9855,7 +9850,7 @@
       <c r="AB73">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AC73" s="8"/>
+      <c r="AC73" s="4"/>
       <c r="AD73" s="4">
         <v>29.8</v>
       </c>
@@ -9927,7 +9922,7 @@
       <c r="AB74">
         <v>1.5</v>
       </c>
-      <c r="AC74" s="8"/>
+      <c r="AC74" s="4"/>
       <c r="AD74" s="4">
         <v>229.1</v>
       </c>
@@ -9999,7 +9994,7 @@
       <c r="AB75">
         <v>1.4</v>
       </c>
-      <c r="AC75" s="8"/>
+      <c r="AC75" s="4"/>
       <c r="AD75" s="4">
         <v>115.7</v>
       </c>
@@ -10071,7 +10066,7 @@
       <c r="AB76">
         <v>2.7</v>
       </c>
-      <c r="AC76" s="8"/>
+      <c r="AC76" s="4"/>
       <c r="AD76" s="4">
         <v>27</v>
       </c>
@@ -10143,7 +10138,7 @@
       <c r="AB77">
         <v>0.9</v>
       </c>
-      <c r="AC77" s="8"/>
+      <c r="AC77" s="4"/>
       <c r="AD77" s="4">
         <v>-176.9</v>
       </c>
@@ -10215,7 +10210,7 @@
       <c r="AB78">
         <v>-0.7</v>
       </c>
-      <c r="AC78" s="8"/>
+      <c r="AC78" s="4"/>
       <c r="AD78" s="4">
         <v>-137</v>
       </c>
@@ -10287,7 +10282,7 @@
       <c r="AB79">
         <v>6.5</v>
       </c>
-      <c r="AC79" s="8"/>
+      <c r="AC79" s="4"/>
       <c r="AD79" s="4">
         <v>-140.19999999999999</v>
       </c>
@@ -10359,7 +10354,7 @@
       <c r="AB80">
         <v>0.3</v>
       </c>
-      <c r="AC80" s="8"/>
+      <c r="AC80" s="4"/>
       <c r="AD80" s="4">
         <v>109</v>
       </c>
@@ -10431,7 +10426,7 @@
       <c r="AB81">
         <v>1</v>
       </c>
-      <c r="AC81" s="8"/>
+      <c r="AC81" s="4"/>
       <c r="AD81" s="4">
         <v>-122.2</v>
       </c>
@@ -10503,7 +10498,7 @@
       <c r="AB82">
         <v>0.2</v>
       </c>
-      <c r="AC82" s="8"/>
+      <c r="AC82" s="4"/>
       <c r="AD82" s="4">
         <v>-50</v>
       </c>
@@ -10575,7 +10570,7 @@
       <c r="AB83">
         <v>0.3</v>
       </c>
-      <c r="AC83" s="8"/>
+      <c r="AC83" s="4"/>
       <c r="AD83" s="4">
         <v>45.8</v>
       </c>
@@ -10647,7 +10642,7 @@
       <c r="AB84">
         <v>-2.2999999999999998</v>
       </c>
-      <c r="AC84" s="8"/>
+      <c r="AC84" s="4"/>
       <c r="AD84" s="4">
         <v>-13.1</v>
       </c>
@@ -10719,7 +10714,7 @@
       <c r="AB85">
         <v>0</v>
       </c>
-      <c r="AC85" s="8"/>
+      <c r="AC85" s="4"/>
       <c r="AD85" s="4">
         <v>52</v>
       </c>
@@ -10791,7 +10786,7 @@
       <c r="AB86">
         <v>-0.6</v>
       </c>
-      <c r="AC86" s="8"/>
+      <c r="AC86" s="4"/>
       <c r="AD86" s="4">
         <v>-3.6</v>
       </c>
@@ -10863,7 +10858,7 @@
       <c r="AB87">
         <v>0.1</v>
       </c>
-      <c r="AC87" s="8"/>
+      <c r="AC87" s="4"/>
       <c r="AD87" s="4">
         <v>114</v>
       </c>
@@ -10935,7 +10930,7 @@
       <c r="AB88">
         <v>-0.5</v>
       </c>
-      <c r="AC88" s="8"/>
+      <c r="AC88" s="4"/>
       <c r="AD88" s="4">
         <v>-184.4</v>
       </c>
@@ -11007,7 +11002,7 @@
       <c r="AB89">
         <v>-1.2</v>
       </c>
-      <c r="AC89" s="8"/>
+      <c r="AC89" s="4"/>
       <c r="AD89" s="4">
         <v>80.099999999999994</v>
       </c>
@@ -11079,7 +11074,7 @@
       <c r="AB90">
         <v>2.4</v>
       </c>
-      <c r="AC90" s="8"/>
+      <c r="AC90" s="4"/>
       <c r="AD90" s="4">
         <v>-66.099999999999994</v>
       </c>
@@ -11151,7 +11146,7 @@
       <c r="AB91">
         <v>0.7</v>
       </c>
-      <c r="AC91" s="8"/>
+      <c r="AC91" s="4"/>
       <c r="AD91" s="4">
         <v>-65</v>
       </c>
@@ -11223,7 +11218,7 @@
       <c r="AB92">
         <v>-0.5</v>
       </c>
-      <c r="AC92" s="8"/>
+      <c r="AC92" s="4"/>
       <c r="AD92" s="4">
         <v>18.8</v>
       </c>
@@ -11295,7 +11290,7 @@
       <c r="AB93">
         <v>0.2</v>
       </c>
-      <c r="AC93" s="8"/>
+      <c r="AC93" s="4"/>
       <c r="AD93" s="4">
         <v>181</v>
       </c>
@@ -11367,7 +11362,7 @@
       <c r="AB94">
         <v>5.8</v>
       </c>
-      <c r="AC94" s="8"/>
+      <c r="AC94" s="4"/>
       <c r="AD94" s="4">
         <v>-162</v>
       </c>
@@ -11439,7 +11434,7 @@
       <c r="AB95">
         <v>-0.6</v>
       </c>
-      <c r="AC95" s="8"/>
+      <c r="AC95" s="4"/>
       <c r="AD95" s="4">
         <v>-362.4</v>
       </c>
@@ -11511,7 +11506,7 @@
       <c r="AB96">
         <v>0.2</v>
       </c>
-      <c r="AC96" s="8"/>
+      <c r="AC96" s="4"/>
       <c r="AD96" s="4">
         <v>-93</v>
       </c>
@@ -11583,7 +11578,7 @@
       <c r="AB97">
         <v>0.6</v>
       </c>
-      <c r="AC97" s="8"/>
+      <c r="AC97" s="4"/>
       <c r="AD97" s="4">
         <v>-76.599999999999994</v>
       </c>
@@ -11655,7 +11650,7 @@
       <c r="AB98">
         <v>-1</v>
       </c>
-      <c r="AC98" s="8"/>
+      <c r="AC98" s="4"/>
       <c r="AD98" s="4">
         <v>16.5</v>
       </c>
@@ -11727,7 +11722,7 @@
       <c r="AB99">
         <v>-0.3</v>
       </c>
-      <c r="AC99" s="8"/>
+      <c r="AC99" s="4"/>
       <c r="AD99" s="4">
         <v>126</v>
       </c>
@@ -11799,7 +11794,7 @@
       <c r="AB100">
         <v>-0.8</v>
       </c>
-      <c r="AC100" s="8"/>
+      <c r="AC100" s="4"/>
       <c r="AD100" s="4">
         <v>-83.7</v>
       </c>
@@ -11871,7 +11866,7 @@
       <c r="AB101">
         <v>0.1</v>
       </c>
-      <c r="AC101" s="8"/>
+      <c r="AC101" s="4"/>
       <c r="AD101" s="4">
         <v>57</v>
       </c>
@@ -11943,7 +11938,7 @@
       <c r="AB102">
         <v>-2</v>
       </c>
-      <c r="AC102" s="8"/>
+      <c r="AC102" s="4"/>
       <c r="AD102" s="4">
         <v>-112.7</v>
       </c>
@@ -12015,7 +12010,7 @@
       <c r="AB103">
         <v>-0.2</v>
       </c>
-      <c r="AC103" s="8"/>
+      <c r="AC103" s="4"/>
       <c r="AD103" s="4">
         <v>59</v>
       </c>
@@ -12087,7 +12082,7 @@
       <c r="AB104">
         <v>-0.3</v>
       </c>
-      <c r="AC104" s="8"/>
+      <c r="AC104" s="4"/>
       <c r="AD104" s="4" t="s">
         <v>109</v>
       </c>
@@ -12159,7 +12154,7 @@
       <c r="AB105">
         <v>1.3</v>
       </c>
-      <c r="AC105" s="8"/>
+      <c r="AC105" s="4"/>
       <c r="AD105" s="4">
         <v>-39.6</v>
       </c>
@@ -12231,7 +12226,7 @@
       <c r="AB106">
         <v>-0.2</v>
       </c>
-      <c r="AC106" s="8"/>
+      <c r="AC106" s="4"/>
       <c r="AD106" s="4" t="s">
         <v>109</v>
       </c>
@@ -12303,7 +12298,7 @@
       <c r="AB107">
         <v>-0.5</v>
       </c>
-      <c r="AC107" s="8"/>
+      <c r="AC107" s="4"/>
       <c r="AD107" s="4">
         <v>-21.1</v>
       </c>
@@ -12375,7 +12370,7 @@
       <c r="AB108">
         <v>1.2</v>
       </c>
-      <c r="AC108" s="8"/>
+      <c r="AC108" s="4"/>
       <c r="AD108" s="4">
         <v>-215.1</v>
       </c>
@@ -12447,7 +12442,7 @@
       <c r="AB109">
         <v>-0.6</v>
       </c>
-      <c r="AC109" s="8"/>
+      <c r="AC109" s="4"/>
       <c r="AD109" s="4">
         <v>206.6</v>
       </c>
@@ -12519,7 +12514,7 @@
       <c r="AB110">
         <v>0.9</v>
       </c>
-      <c r="AC110" s="8"/>
+      <c r="AC110" s="4"/>
       <c r="AD110" s="4">
         <v>31</v>
       </c>
@@ -12591,7 +12586,7 @@
       <c r="AB111">
         <v>-0.3</v>
       </c>
-      <c r="AC111" s="8"/>
+      <c r="AC111" s="4"/>
       <c r="AD111" s="4">
         <v>-17.7</v>
       </c>
@@ -12663,7 +12658,7 @@
       <c r="AB112">
         <v>-0.1</v>
       </c>
-      <c r="AC112" s="8"/>
+      <c r="AC112" s="4"/>
       <c r="AD112" s="4">
         <v>-27.3</v>
       </c>
@@ -12735,7 +12730,7 @@
       <c r="AB113">
         <v>-1.5</v>
       </c>
-      <c r="AC113" s="8"/>
+      <c r="AC113" s="4"/>
       <c r="AD113" s="4">
         <v>-158.69999999999999</v>
       </c>
@@ -12807,7 +12802,7 @@
       <c r="AB114">
         <v>0</v>
       </c>
-      <c r="AC114" s="8"/>
+      <c r="AC114" s="4"/>
       <c r="AD114" s="4" t="s">
         <v>109</v>
       </c>
@@ -12879,7 +12874,7 @@
       <c r="AB115">
         <v>-4.7</v>
       </c>
-      <c r="AC115" s="8"/>
+      <c r="AC115" s="4"/>
       <c r="AD115" s="4" t="s">
         <v>109</v>
       </c>
@@ -12951,7 +12946,7 @@
       <c r="AB116">
         <v>-0.3</v>
       </c>
-      <c r="AC116" s="8"/>
+      <c r="AC116" s="4"/>
       <c r="AD116" s="4">
         <v>-3.2</v>
       </c>
@@ -13023,7 +13018,7 @@
       <c r="AB117">
         <v>-0.1</v>
       </c>
-      <c r="AC117" s="8"/>
+      <c r="AC117" s="4"/>
       <c r="AD117" s="4">
         <v>-238</v>
       </c>
@@ -13095,7 +13090,7 @@
       <c r="AB118">
         <v>-0.8</v>
       </c>
-      <c r="AC118" s="8"/>
+      <c r="AC118" s="4"/>
       <c r="AD118" s="4">
         <v>-197.2</v>
       </c>
@@ -13167,7 +13162,7 @@
       <c r="AB119">
         <v>0.5</v>
       </c>
-      <c r="AC119" s="8"/>
+      <c r="AC119" s="4"/>
       <c r="AD119" s="4">
         <v>155.69999999999999</v>
       </c>
@@ -13239,7 +13234,7 @@
       <c r="AB120">
         <v>-0.2</v>
       </c>
-      <c r="AC120" s="8"/>
+      <c r="AC120" s="4"/>
       <c r="AD120" s="4">
         <v>94.1</v>
       </c>
@@ -13311,7 +13306,7 @@
       <c r="AB121">
         <v>-1.3</v>
       </c>
-      <c r="AC121" s="8"/>
+      <c r="AC121" s="4"/>
       <c r="AD121" s="4">
         <v>-28.1</v>
       </c>
@@ -13383,7 +13378,7 @@
       <c r="AB122">
         <v>-0.6</v>
       </c>
-      <c r="AC122" s="8"/>
+      <c r="AC122" s="4"/>
       <c r="AD122" s="4" t="s">
         <v>109</v>
       </c>
@@ -13455,7 +13450,7 @@
       <c r="AB123">
         <v>-0.1</v>
       </c>
-      <c r="AC123" s="8"/>
+      <c r="AC123" s="4"/>
       <c r="AD123" s="4" t="s">
         <v>109</v>
       </c>
@@ -13527,7 +13522,7 @@
       <c r="AB124">
         <v>-3.8</v>
       </c>
-      <c r="AC124" s="8"/>
+      <c r="AC124" s="4"/>
       <c r="AD124" s="4">
         <v>222.9</v>
       </c>
@@ -13599,7 +13594,7 @@
       <c r="AB125">
         <v>-1.1000000000000001</v>
       </c>
-      <c r="AC125" s="8"/>
+      <c r="AC125" s="4"/>
       <c r="AD125" s="4">
         <v>53.9</v>
       </c>
@@ -13671,7 +13666,7 @@
       <c r="AB126">
         <v>-0.5</v>
       </c>
-      <c r="AC126" s="8"/>
+      <c r="AC126" s="4"/>
       <c r="AD126" s="4">
         <v>17</v>
       </c>
@@ -13743,7 +13738,7 @@
       <c r="AB127">
         <v>-1.2</v>
       </c>
-      <c r="AC127" s="8"/>
+      <c r="AC127" s="4"/>
       <c r="AD127" s="4">
         <v>18.100000000000001</v>
       </c>
@@ -13815,7 +13810,7 @@
       <c r="AB128">
         <v>-1.6</v>
       </c>
-      <c r="AC128" s="8"/>
+      <c r="AC128" s="4"/>
       <c r="AD128" s="4">
         <v>39.9</v>
       </c>
@@ -13887,7 +13882,7 @@
       <c r="AB129">
         <v>-0.9</v>
       </c>
-      <c r="AC129" s="8"/>
+      <c r="AC129" s="4"/>
       <c r="AD129" s="4">
         <v>-57.2</v>
       </c>
@@ -13959,7 +13954,7 @@
       <c r="AB130">
         <v>-2</v>
       </c>
-      <c r="AC130" s="8"/>
+      <c r="AC130" s="4"/>
       <c r="AD130" s="4">
         <v>-111.7</v>
       </c>
@@ -14031,7 +14026,7 @@
       <c r="AB131">
         <v>-0.4</v>
       </c>
-      <c r="AC131" s="8"/>
+      <c r="AC131" s="4"/>
       <c r="AD131" s="4">
         <v>-146.30000000000001</v>
       </c>
@@ -14103,7 +14098,7 @@
       <c r="AB132">
         <v>-1.5</v>
       </c>
-      <c r="AC132" s="8"/>
+      <c r="AC132" s="4"/>
       <c r="AD132" s="4">
         <v>-43</v>
       </c>
@@ -14175,7 +14170,7 @@
       <c r="AB133">
         <v>-2</v>
       </c>
-      <c r="AC133" s="8"/>
+      <c r="AC133" s="4"/>
       <c r="AD133" s="4">
         <v>220.3</v>
       </c>
@@ -14247,7 +14242,7 @@
       <c r="AB134">
         <v>0</v>
       </c>
-      <c r="AC134" s="8"/>
+      <c r="AC134" s="4"/>
       <c r="AD134" s="4" t="s">
         <v>109</v>
       </c>
@@ -14319,7 +14314,7 @@
       <c r="AB135">
         <v>-0.5</v>
       </c>
-      <c r="AC135" s="8"/>
+      <c r="AC135" s="4"/>
       <c r="AD135" s="4">
         <v>-107.6</v>
       </c>
@@ -14391,7 +14386,7 @@
       <c r="AB136">
         <v>-6.5</v>
       </c>
-      <c r="AC136" s="8"/>
+      <c r="AC136" s="4"/>
       <c r="AD136" s="4">
         <v>141.30000000000001</v>
       </c>
@@ -14463,7 +14458,7 @@
       <c r="AB137">
         <v>-1.3</v>
       </c>
-      <c r="AC137" s="8"/>
+      <c r="AC137" s="4"/>
       <c r="AD137" s="4">
         <v>22.8</v>
       </c>
@@ -14535,7 +14530,7 @@
       <c r="AB138">
         <v>-2.6</v>
       </c>
-      <c r="AC138" s="8"/>
+      <c r="AC138" s="4"/>
       <c r="AD138" s="4">
         <v>-94.5</v>
       </c>
@@ -14607,7 +14602,7 @@
       <c r="AB139">
         <v>-0.3</v>
       </c>
-      <c r="AC139" s="8"/>
+      <c r="AC139" s="4"/>
       <c r="AD139" s="4">
         <v>-61.7</v>
       </c>
@@ -14679,7 +14674,7 @@
       <c r="AB140">
         <v>-1.7</v>
       </c>
-      <c r="AC140" s="8"/>
+      <c r="AC140" s="4"/>
       <c r="AD140" s="4">
         <v>-26.7</v>
       </c>
@@ -14751,7 +14746,7 @@
       <c r="AB141">
         <v>-0.5</v>
       </c>
-      <c r="AC141" s="8"/>
+      <c r="AC141" s="4"/>
       <c r="AD141" s="4">
         <v>-27.5</v>
       </c>
@@ -14823,7 +14818,7 @@
       <c r="AB142">
         <v>1.4</v>
       </c>
-      <c r="AC142" s="8"/>
+      <c r="AC142" s="4"/>
       <c r="AD142" s="4">
         <v>-135.6</v>
       </c>
@@ -14895,7 +14890,7 @@
       <c r="AB143">
         <v>-7.8</v>
       </c>
-      <c r="AC143" s="8"/>
+      <c r="AC143" s="4"/>
       <c r="AD143" s="4">
         <v>166</v>
       </c>
@@ -14967,7 +14962,7 @@
       <c r="AB144">
         <v>0.3</v>
       </c>
-      <c r="AC144" s="8"/>
+      <c r="AC144" s="4"/>
       <c r="AD144" s="4">
         <v>-31.7</v>
       </c>
@@ -15039,7 +15034,7 @@
       <c r="AB145">
         <v>-10.199999999999999</v>
       </c>
-      <c r="AC145" s="8"/>
+      <c r="AC145" s="4"/>
       <c r="AD145" s="4">
         <v>115</v>
       </c>
@@ -15111,7 +15106,7 @@
       <c r="AB146">
         <v>-2.1</v>
       </c>
-      <c r="AC146" s="8"/>
+      <c r="AC146" s="4"/>
       <c r="AD146" s="4">
         <v>174.7</v>
       </c>
@@ -15183,7 +15178,7 @@
       <c r="AB147">
         <v>-10.9</v>
       </c>
-      <c r="AC147" s="8"/>
+      <c r="AC147" s="4"/>
       <c r="AD147" s="4">
         <v>130</v>
       </c>
@@ -15255,7 +15250,7 @@
       <c r="AB148">
         <v>-3.6</v>
       </c>
-      <c r="AC148" s="8"/>
+      <c r="AC148" s="4"/>
       <c r="AD148" s="4">
         <v>-68</v>
       </c>
@@ -15327,7 +15322,7 @@
       <c r="AB149">
         <v>-0.3</v>
       </c>
-      <c r="AC149" s="8"/>
+      <c r="AC149" s="4"/>
       <c r="AD149" s="4">
         <v>-22.8</v>
       </c>
@@ -15399,7 +15394,7 @@
       <c r="AB150">
         <v>-9.1</v>
       </c>
-      <c r="AC150" s="8"/>
+      <c r="AC150" s="4"/>
       <c r="AD150" s="4">
         <v>-189.3</v>
       </c>
@@ -15471,7 +15466,7 @@
       <c r="AB151">
         <v>-5.0999999999999996</v>
       </c>
-      <c r="AC151" s="8"/>
+      <c r="AC151" s="4"/>
       <c r="AD151" s="4">
         <v>-411.4</v>
       </c>
@@ -15543,7 +15538,7 @@
       <c r="AB152">
         <v>-9.1999999999999993</v>
       </c>
-      <c r="AC152" s="8"/>
+      <c r="AC152" s="4"/>
       <c r="AD152" s="4">
         <v>-345</v>
       </c>
@@ -15615,7 +15610,7 @@
       <c r="AB153">
         <v>-13.7</v>
       </c>
-      <c r="AC153" s="8"/>
+      <c r="AC153" s="4"/>
       <c r="AD153" s="4">
         <v>-384.1</v>
       </c>
@@ -15687,7 +15682,7 @@
       <c r="AB154">
         <v>-4.8</v>
       </c>
-      <c r="AC154" s="8"/>
+      <c r="AC154" s="4"/>
       <c r="AD154" s="4">
         <v>-107</v>
       </c>
@@ -15759,7 +15754,7 @@
       <c r="AB155">
         <v>-6.7</v>
       </c>
-      <c r="AC155" s="8"/>
+      <c r="AC155" s="4"/>
       <c r="AD155" s="4">
         <v>-5.3</v>
       </c>
@@ -15831,7 +15826,7 @@
       <c r="AB156">
         <v>-5.9</v>
       </c>
-      <c r="AC156" s="8"/>
+      <c r="AC156" s="4"/>
       <c r="AD156" s="4">
         <v>-184.2</v>
       </c>
@@ -15903,7 +15898,7 @@
       <c r="AB157">
         <v>-14.1</v>
       </c>
-      <c r="AC157" s="8"/>
+      <c r="AC157" s="4"/>
       <c r="AD157" s="4">
         <v>27.8</v>
       </c>
@@ -15975,7 +15970,7 @@
       <c r="AB158">
         <v>-17.600000000000001</v>
       </c>
-      <c r="AC158" s="8"/>
+      <c r="AC158" s="4"/>
       <c r="AD158" s="4">
         <v>25.2</v>
       </c>
@@ -16047,7 +16042,7 @@
       <c r="AB159">
         <v>-23.5</v>
       </c>
-      <c r="AC159" s="8"/>
+      <c r="AC159" s="4"/>
       <c r="AD159" s="4">
         <v>-177.5</v>
       </c>

--- a/all data.xlsx
+++ b/all data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dperez/Documents/2026/Term 3/Astrophysics/GitHub/phys3116assignment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A7826E4-2412-0E41-A24D-2406165781B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{597CACDF-F5D1-C447-8D27-5A7914D4A528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16940" xr2:uid="{75C62DBF-A087-234F-B939-43CA23AF865F}"/>
   </bookViews>
@@ -353,9 +353,6 @@
     <t>r_h</t>
   </si>
   <si>
-    <t>mu_V</t>
-  </si>
-  <si>
     <t>rho_0</t>
   </si>
   <si>
@@ -1356,6 +1353,9 @@
   </si>
   <si>
     <t>harrispartI</t>
+  </si>
+  <si>
+    <t>vsi</t>
   </si>
 </sst>
 </file>
@@ -1764,7 +1764,7 @@
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -1772,7 +1772,7 @@
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
@@ -1786,7 +1786,7 @@
       <c r="Q1" s="6"/>
       <c r="R1" s="6"/>
       <c r="S1" s="6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="T1" s="6"/>
       <c r="U1" s="6"/>
@@ -1798,7 +1798,7 @@
       <c r="AA1" s="6"/>
       <c r="AB1" s="6"/>
       <c r="AD1" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AE1" s="6"/>
       <c r="AF1" s="6"/>
@@ -1832,7 +1832,7 @@
         <v>5</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2" t="s">
         <v>5</v>
@@ -1868,34 +1868,34 @@
         <v>75</v>
       </c>
       <c r="S2" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="T2" t="s">
+        <v>109</v>
+      </c>
+      <c r="U2" t="s">
         <v>110</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>111</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>112</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>113</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>114</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>115</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" t="s">
         <v>116</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AB2" t="s">
         <v>117</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>118</v>
       </c>
       <c r="AC2" s="4"/>
       <c r="AD2" s="4" t="s">
@@ -1923,16 +1923,16 @@
         <v>104</v>
       </c>
       <c r="AL2" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="AM2" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="AM2" s="4" t="s">
+      <c r="AN2" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="AN2" s="4" t="s">
+      <c r="AO2" s="4" t="s">
         <v>107</v>
-      </c>
-      <c r="AO2" s="4" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.2">
@@ -1991,13 +1991,13 @@
         <v>5.0609999999999999</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="T3" s="2">
         <v>1.6732291666666666E-2</v>
       </c>
       <c r="U3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="V3">
         <v>305.89</v>
@@ -2111,13 +2111,13 @@
         <v>2.9529999999999998</v>
       </c>
       <c r="S4" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="T4" s="2">
         <v>3.6634722222222221E-2</v>
       </c>
       <c r="U4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="V4">
         <v>152.30000000000001</v>
@@ -2234,13 +2234,13 @@
         <v>4.9379999999999997</v>
       </c>
       <c r="S5" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="T5" s="2">
         <v>4.3915046296296299E-2</v>
       </c>
       <c r="U5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V5">
         <v>301.52999999999997</v>
@@ -2357,13 +2357,13 @@
         <v>3.9129999999999998</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="T6" s="3">
         <v>8.5381944444444441E-2</v>
       </c>
       <c r="U6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="V6">
         <v>161.22</v>
@@ -2397,10 +2397,10 @@
         <v>-138.1</v>
       </c>
       <c r="AG6" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH6" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI6" s="4">
         <v>0.55000000000000004</v>
@@ -2412,13 +2412,13 @@
         <v>0.22</v>
       </c>
       <c r="AL6" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM6" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AN6" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AO6" s="4">
         <v>7.93</v>
@@ -2480,13 +2480,13 @@
         <v>5.1360000000000001</v>
       </c>
       <c r="S7" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="T7" s="2">
         <v>0.13352094907407405</v>
       </c>
       <c r="U7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="V7">
         <v>270.54000000000002</v>
@@ -2520,10 +2520,10 @@
         <v>54.9</v>
       </c>
       <c r="AG7" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH7" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI7" s="4">
         <v>1.1599999999999999</v>
@@ -2603,13 +2603,13 @@
         <v>5.07</v>
       </c>
       <c r="S8" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="T8" s="2">
         <v>0.14814861111111113</v>
       </c>
       <c r="U8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="V8">
         <v>130.06</v>
@@ -2643,10 +2643,10 @@
         <v>-76.2</v>
       </c>
       <c r="AG8" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH8" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI8" s="4">
         <v>2.57</v>
@@ -2726,13 +2726,13 @@
         <v>3.5990000000000002</v>
       </c>
       <c r="S9" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="T9" s="2">
         <v>0.1632210648148148</v>
       </c>
       <c r="U9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="V9">
         <v>258.33999999999997</v>
@@ -2766,10 +2766,10 @@
         <v>101.3</v>
       </c>
       <c r="AG9" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH9" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI9" s="4">
         <v>1.36</v>
@@ -2849,13 +2849,13 @@
         <v>3.8860000000000001</v>
       </c>
       <c r="S10" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="T10" s="2">
         <v>0.18384837962962963</v>
       </c>
       <c r="U10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="V10">
         <v>218.1</v>
@@ -2889,10 +2889,10 @@
         <v>-39.1</v>
       </c>
       <c r="AG10" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH10" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI10" s="4">
         <v>1.1000000000000001</v>
@@ -2972,13 +2972,13 @@
         <v>3.5590000000000002</v>
       </c>
       <c r="S11" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="T11" s="2">
         <v>0.19867951388888888</v>
       </c>
       <c r="U11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="V11">
         <v>170.53</v>
@@ -3012,10 +3012,10 @@
         <v>-140.1</v>
       </c>
       <c r="AG11" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH11" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI11" s="4">
         <v>1.53</v>
@@ -3092,13 +3092,13 @@
         <v>3.8849999999999998</v>
       </c>
       <c r="S12" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="T12" s="2">
         <v>0.21813379629629628</v>
       </c>
       <c r="U12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="V12">
         <v>244.51</v>
@@ -3215,13 +3215,13 @@
         <v>3.8660000000000001</v>
       </c>
       <c r="S13" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="T13" s="2">
         <v>0.2251283564814815</v>
       </c>
       <c r="U13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="V13">
         <v>227.23</v>
@@ -3338,13 +3338,13 @@
         <v>2.1960000000000002</v>
       </c>
       <c r="S14" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="T14" s="2">
         <v>0.28402094907407405</v>
       </c>
       <c r="U14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="V14">
         <v>245.63</v>
@@ -3378,10 +3378,10 @@
         <v>132</v>
       </c>
       <c r="AG14" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH14" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI14" s="4">
         <v>1.38</v>
@@ -3458,13 +3458,13 @@
         <v>4.2539999999999996</v>
       </c>
       <c r="S15" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="T15" s="2">
         <v>0.318153587962963</v>
       </c>
       <c r="U15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="V15">
         <v>180.37</v>
@@ -3581,13 +3581,13 @@
         <v>4.6280000000000001</v>
       </c>
       <c r="S16" s="5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="T16" s="2">
         <v>0.3321412037037037</v>
       </c>
       <c r="U16" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="V16">
         <v>195.12</v>
@@ -3612,19 +3612,19 @@
       </c>
       <c r="AC16" s="4"/>
       <c r="AD16" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AE16" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF16" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG16" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH16" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI16" s="4">
         <v>0.5</v>
@@ -3636,13 +3636,13 @@
         <v>0.21</v>
       </c>
       <c r="AL16" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM16" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AN16" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AO16" s="4">
         <v>7.7</v>
@@ -3704,13 +3704,13 @@
         <v>2.4529999999999998</v>
       </c>
       <c r="S17" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="T17" s="2">
         <v>0.38053009259259263</v>
       </c>
       <c r="U17" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="V17">
         <v>261.32</v>
@@ -3744,31 +3744,31 @@
         <v>20.7</v>
       </c>
       <c r="AG17" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH17" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI17" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AJ17" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK17" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AL17" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM17" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AN17" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AO17" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" spans="1:41" x14ac:dyDescent="0.2">
@@ -3827,13 +3827,13 @@
         <v>4.4569999999999999</v>
       </c>
       <c r="S18" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="T18" s="2">
         <v>0.38336921296296295</v>
       </c>
       <c r="U18" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="V18">
         <v>282.19</v>
@@ -3950,13 +3950,13 @@
         <v>4.1559999999999997</v>
       </c>
       <c r="S19" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="T19" s="2">
         <v>0.38954942129629627</v>
       </c>
       <c r="U19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V19">
         <v>292.27</v>
@@ -3981,19 +3981,19 @@
       </c>
       <c r="AC19" s="4"/>
       <c r="AD19" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AE19" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF19" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG19" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH19" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI19" s="4">
         <v>0.75</v>
@@ -4070,13 +4070,13 @@
         <v>4.2590000000000003</v>
       </c>
       <c r="S20" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="T20" s="2">
         <v>0.42050810185185189</v>
       </c>
       <c r="U20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="V20">
         <v>240.15</v>
@@ -4110,10 +4110,10 @@
         <v>75.900000000000006</v>
       </c>
       <c r="AG20" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH20" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI20" s="4">
         <v>0.99</v>
@@ -4190,13 +4190,13 @@
         <v>2.98</v>
       </c>
       <c r="S21" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="T21" s="2">
         <v>0.42889837962962962</v>
       </c>
       <c r="U21" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="V21">
         <v>277.23</v>
@@ -4313,13 +4313,13 @@
         <v>4.07</v>
       </c>
       <c r="S22" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="T22" s="2">
         <v>0.47866666666666668</v>
       </c>
       <c r="U22" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="V22">
         <v>202.31</v>
@@ -4353,10 +4353,10 @@
         <v>76.599999999999994</v>
       </c>
       <c r="AG22" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH22" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI22" s="4">
         <v>0.93</v>
@@ -4433,13 +4433,13 @@
         <v>2.9750000000000001</v>
       </c>
       <c r="S23" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="T23" s="2">
         <v>0.49951967592592594</v>
       </c>
       <c r="U23" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="V23">
         <v>260.99</v>
@@ -4464,19 +4464,19 @@
       </c>
       <c r="AC23" s="4"/>
       <c r="AD23" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AE23" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF23" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG23" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH23" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI23" s="4">
         <v>0.5</v>
@@ -4488,13 +4488,13 @@
         <v>0.26</v>
       </c>
       <c r="AL23" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM23" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AN23" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AO23" s="4">
         <v>8.6199999999999992</v>
@@ -4553,13 +4553,13 @@
         <v>3.8319999999999999</v>
       </c>
       <c r="S24" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="T24" s="2">
         <v>0.50701736111111118</v>
       </c>
       <c r="U24" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="V24">
         <v>252.85</v>
@@ -4673,13 +4673,13 @@
         <v>4.2190000000000003</v>
       </c>
       <c r="S25" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="T25" s="2">
         <v>0.51788657407407412</v>
       </c>
       <c r="U25" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="V25">
         <v>300.99</v>
@@ -4713,10 +4713,10 @@
         <v>64.2</v>
       </c>
       <c r="AG25" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH25" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI25" s="4">
         <v>1.3</v>
@@ -4793,13 +4793,13 @@
         <v>3.9609999999999999</v>
       </c>
       <c r="S26" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="T26" s="2">
         <v>0.52685416666666662</v>
       </c>
       <c r="U26" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="V26">
         <v>300.88</v>
@@ -4833,10 +4833,10 @@
         <v>-49.7</v>
       </c>
       <c r="AG26" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH26" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI26" s="4">
         <v>0.7</v>
@@ -4913,13 +4913,13 @@
         <v>4.1120000000000001</v>
       </c>
       <c r="S27" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="T27" s="2">
         <v>0.52740717592592601</v>
       </c>
       <c r="U27" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="V27">
         <v>299.63</v>
@@ -5036,13 +5036,13 @@
         <v>4.6559999999999997</v>
       </c>
       <c r="S28" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="T28" s="2">
         <v>0.5413648148148148</v>
       </c>
       <c r="U28" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="V28">
         <v>303.60000000000002</v>
@@ -5076,10 +5076,10 @@
         <v>192.9</v>
       </c>
       <c r="AG28" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH28" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI28" s="4">
         <v>1.25</v>
@@ -5159,13 +5159,13 @@
         <v>4.6180000000000003</v>
       </c>
       <c r="S29" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="T29" s="2">
         <v>0.55063946759259264</v>
       </c>
       <c r="U29" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="V29">
         <v>332.96</v>
@@ -5282,13 +5282,13 @@
         <v>3.5920000000000001</v>
       </c>
       <c r="S30" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="T30" s="2">
         <v>0.55309131944444445</v>
       </c>
       <c r="U30" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="V30">
         <v>335.7</v>
@@ -5405,13 +5405,13 @@
         <v>3.2610000000000001</v>
       </c>
       <c r="S31" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="T31" s="2">
         <v>0.56026898148148141</v>
       </c>
       <c r="U31" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="V31">
         <v>309.10000000000002</v>
@@ -5528,13 +5528,13 @@
         <v>3.1349999999999998</v>
       </c>
       <c r="S32" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="T32" s="2">
         <v>0.57096782407407409</v>
       </c>
       <c r="U32" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="V32">
         <v>42.22</v>
@@ -5651,13 +5651,13 @@
         <v>5.7590000000000003</v>
       </c>
       <c r="S33" s="5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="T33" s="2">
         <v>0.57392141203703706</v>
       </c>
       <c r="U33" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="V33">
         <v>311.61</v>
@@ -5774,13 +5774,13 @@
         <v>3.4590000000000001</v>
       </c>
       <c r="S34" s="5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="T34" s="2">
         <v>0.58080671296296293</v>
       </c>
       <c r="U34" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="V34">
         <v>320.27999999999997</v>
@@ -5805,19 +5805,19 @@
       </c>
       <c r="AC34" s="4"/>
       <c r="AD34" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AE34" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF34" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG34" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH34" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI34" s="4">
         <v>0.7</v>
@@ -5894,13 +5894,13 @@
         <v>3.327</v>
       </c>
       <c r="S35" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="T35" s="2">
         <v>0.58712141203703705</v>
       </c>
       <c r="U35" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="V35">
         <v>42.15</v>
@@ -6014,13 +6014,13 @@
         <v>5.0190000000000001</v>
       </c>
       <c r="S36" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="T36" s="2">
         <v>0.60390312499999999</v>
       </c>
       <c r="U36" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="V36">
         <v>342.21</v>
@@ -6054,10 +6054,10 @@
         <v>-37.5</v>
       </c>
       <c r="AG36" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH36" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI36" s="4">
         <v>2.0699999999999998</v>
@@ -6134,13 +6134,13 @@
         <v>4.1120000000000001</v>
       </c>
       <c r="S37" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="T37" s="2">
         <v>0.61083668981481487</v>
       </c>
       <c r="U37" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="V37">
         <v>331.06</v>
@@ -6257,13 +6257,13 @@
         <v>4.8689999999999998</v>
       </c>
       <c r="S38" s="5" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="T38" s="2">
         <v>0.62521354166666665</v>
       </c>
       <c r="U38" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="V38">
         <v>307.35000000000002</v>
@@ -6380,13 +6380,13 @@
         <v>4.3079999999999998</v>
       </c>
       <c r="S39" s="5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="T39" s="2">
         <v>0.62776192129629627</v>
       </c>
       <c r="U39" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="V39">
         <v>332.56</v>
@@ -6503,13 +6503,13 @@
         <v>4.5830000000000002</v>
       </c>
       <c r="S40" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="T40" s="2">
         <v>0.63617187500000005</v>
       </c>
       <c r="U40" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="V40">
         <v>0.85</v>
@@ -6623,13 +6623,13 @@
         <v>4.3109999999999999</v>
       </c>
       <c r="S41" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="T41" s="2">
         <v>0.63708912037037035</v>
       </c>
       <c r="U41" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="V41">
         <v>342.95</v>
@@ -6663,10 +6663,10 @@
         <v>108.4</v>
       </c>
       <c r="AG41" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH41" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI41" s="4">
         <v>0.86</v>
@@ -6743,13 +6743,13 @@
         <v>5.21</v>
       </c>
       <c r="S42" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="T42" s="2">
         <v>0.63788449074074072</v>
       </c>
       <c r="U42" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="V42">
         <v>3.86</v>
@@ -6863,13 +6863,13 @@
         <v>4.968</v>
       </c>
       <c r="S43" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="T43" s="2">
         <v>0.64445243055555557</v>
       </c>
       <c r="U43" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="V43">
         <v>326.60000000000002</v>
@@ -6903,10 +6903,10 @@
         <v>-107.2</v>
       </c>
       <c r="AG43" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH43" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI43" s="4">
         <v>1.6</v>
@@ -6983,13 +6983,13 @@
         <v>4.4580000000000002</v>
       </c>
       <c r="S44" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="T44" s="2">
         <v>0.64963564814814811</v>
       </c>
       <c r="U44" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="V44">
         <v>327.58</v>
@@ -7106,13 +7106,13 @@
         <v>3.7549999999999999</v>
       </c>
       <c r="S45" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="T45" s="2">
         <v>0.65216956018518513</v>
       </c>
       <c r="U45" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="V45">
         <v>328.41</v>
@@ -7137,19 +7137,19 @@
       </c>
       <c r="AC45" s="4"/>
       <c r="AD45" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AE45" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF45" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG45" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH45" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI45" s="4">
         <v>0.85</v>
@@ -7226,13 +7226,13 @@
         <v>4.6550000000000002</v>
       </c>
       <c r="S46" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="T46" s="2">
         <v>0.65697916666666667</v>
       </c>
       <c r="U46" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="V46">
         <v>337.02</v>
@@ -7266,10 +7266,10 @@
         <v>92.9</v>
       </c>
       <c r="AG46" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH46" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI46" s="4">
         <v>1.23</v>
@@ -7346,13 +7346,13 @@
         <v>3.9049999999999998</v>
       </c>
       <c r="S47" s="5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="T47" s="2">
         <v>0.67434780092592594</v>
       </c>
       <c r="U47" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="V47">
         <v>328.77</v>
@@ -7386,10 +7386,10 @@
         <v>8</v>
       </c>
       <c r="AG47" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH47" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI47" s="4">
         <v>0.95</v>
@@ -7401,13 +7401,13 @@
         <v>1.2</v>
       </c>
       <c r="AL47" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM47" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AN47" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AO47" s="4">
         <v>8.83</v>
@@ -7469,13 +7469,13 @@
         <v>3.5150000000000001</v>
       </c>
       <c r="S48" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="T48" s="2">
         <v>0.67431249999999998</v>
       </c>
       <c r="U48" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="V48">
         <v>28.74</v>
@@ -7592,13 +7592,13 @@
         <v>3.746</v>
       </c>
       <c r="S49" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="T49" s="2">
         <v>0.67850011574074076</v>
       </c>
       <c r="U49" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="V49">
         <v>352.67</v>
@@ -7715,13 +7715,13 @@
         <v>3.9980000000000002</v>
       </c>
       <c r="S50" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="T50" s="2">
         <v>0.68304652777777775</v>
       </c>
       <c r="U50" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="V50">
         <v>350.97</v>
@@ -7838,13 +7838,13 @@
         <v>3.3039999999999998</v>
       </c>
       <c r="S51" s="5" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="T51" s="2">
         <v>0.68458472222222222</v>
       </c>
       <c r="U51" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="V51">
         <v>317.74</v>
@@ -7878,10 +7878,10 @@
         <v>357</v>
       </c>
       <c r="AG51" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH51" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI51" s="4">
         <v>0.8</v>
@@ -7961,13 +7961,13 @@
         <v>4.827</v>
       </c>
       <c r="S52" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="T52" s="2">
         <v>0.68557708333333334</v>
       </c>
       <c r="U52" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="V52">
         <v>351.93</v>
@@ -8001,10 +8001,10 @@
         <v>201.9</v>
       </c>
       <c r="AG52" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH52" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI52" s="4">
         <v>1.55</v>
@@ -8084,13 +8084,13 @@
         <v>4.5309999999999997</v>
       </c>
       <c r="S53" s="5" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="T53" s="2">
         <v>0.68588391203703702</v>
       </c>
       <c r="U53" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="V53">
         <v>342.37</v>
@@ -8124,10 +8124,10 @@
         <v>11.5</v>
       </c>
       <c r="AG53" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH53" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI53" s="4">
         <v>1.86</v>
@@ -8207,13 +8207,13 @@
         <v>4.8310000000000004</v>
       </c>
       <c r="S54" s="5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="T54" s="2">
         <v>0.68657500000000005</v>
       </c>
       <c r="U54" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="V54">
         <v>345.08</v>
@@ -8247,10 +8247,10 @@
         <v>-130.6</v>
       </c>
       <c r="AG54" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH54" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI54" s="4">
         <v>0.7</v>
@@ -8294,7 +8294,7 @@
         <v>-0.82</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H55">
         <v>-1.74</v>
@@ -8327,13 +8327,13 @@
         <v>1.5449999999999999</v>
       </c>
       <c r="S55" s="5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="T55" s="2">
         <v>0.68925763888888891</v>
       </c>
       <c r="U55" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="V55">
         <v>3.37</v>
@@ -8414,7 +8414,7 @@
         <v>-1.32</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H56">
         <v>-0.81</v>
@@ -8447,13 +8447,13 @@
         <v>3.2970000000000002</v>
       </c>
       <c r="S56" s="5" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="T56" s="2">
         <v>0.69404456018518512</v>
       </c>
       <c r="U56" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V56">
         <v>351.91</v>
@@ -8478,19 +8478,19 @@
       </c>
       <c r="AC56" s="4"/>
       <c r="AD56" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AE56" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF56" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG56" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH56" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI56" s="4">
         <v>1</v>
@@ -8534,7 +8534,7 @@
         <v>-1.21</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H57">
         <v>-2.34</v>
@@ -8567,13 +8567,13 @@
         <v>1.9379999999999999</v>
       </c>
       <c r="S57" s="5" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="T57" s="2">
         <v>0.69561620370370369</v>
       </c>
       <c r="U57" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="V57">
         <v>59.01</v>
@@ -8656,13 +8656,13 @@
       <c r="G58" s="5"/>
       <c r="P58" s="2"/>
       <c r="S58" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="T58" s="2">
         <v>0.69929155092592599</v>
       </c>
       <c r="U58" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="V58">
         <v>73.64</v>
@@ -8696,10 +8696,10 @@
         <v>-138.4</v>
       </c>
       <c r="AG58" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH58" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI58" s="4">
         <v>1.5</v>
@@ -8745,13 +8745,13 @@
       <c r="G59" s="5"/>
       <c r="P59" s="2"/>
       <c r="S59" s="5" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="T59" s="2">
         <v>0.6994696759259259</v>
       </c>
       <c r="U59" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="V59">
         <v>15.72</v>
@@ -8834,13 +8834,13 @@
       <c r="G60" s="5"/>
       <c r="P60" s="2"/>
       <c r="S60" s="5" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="T60" s="2">
         <v>0.70290046296296294</v>
       </c>
       <c r="U60" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="V60">
         <v>339.19</v>
@@ -8865,19 +8865,19 @@
       </c>
       <c r="AC60" s="4"/>
       <c r="AD60" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AE60" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF60" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG60" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH60" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI60" s="4">
         <v>0.56000000000000005</v>
@@ -8889,13 +8889,13 @@
         <v>0.34</v>
       </c>
       <c r="AL60" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM60" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AN60" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AO60" s="4">
         <v>8.11</v>
@@ -8923,13 +8923,13 @@
       <c r="G61" s="5"/>
       <c r="P61" s="2"/>
       <c r="S61" s="5" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="T61" s="2">
         <v>0.70376516203703698</v>
       </c>
       <c r="U61" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="V61">
         <v>358.92</v>
@@ -8963,10 +8963,10 @@
         <v>96.8</v>
       </c>
       <c r="AG61" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH61" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI61" s="4">
         <v>1.53</v>
@@ -9012,13 +9012,13 @@
       <c r="G62" s="5"/>
       <c r="P62" s="2"/>
       <c r="S62" s="5" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="T62" s="2">
         <v>0.70635474537037035</v>
       </c>
       <c r="U62" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="V62">
         <v>15.14</v>
@@ -9101,13 +9101,13 @@
       <c r="G63" s="5"/>
       <c r="P63" s="2"/>
       <c r="S63" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="T63" s="2">
         <v>0.7080164351851852</v>
       </c>
       <c r="U63" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="V63">
         <v>347.79</v>
@@ -9173,13 +9173,13 @@
       <c r="G64" s="5"/>
       <c r="P64" s="2"/>
       <c r="S64" s="5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="T64" s="2">
         <v>0.70822916666666669</v>
       </c>
       <c r="U64" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="V64">
         <v>18.88</v>
@@ -9213,10 +9213,10 @@
         <v>82.9</v>
       </c>
       <c r="AG64" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH64" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI64" s="4">
         <v>0.6</v>
@@ -9245,13 +9245,13 @@
       <c r="G65" s="5"/>
       <c r="P65" s="2"/>
       <c r="S65" s="5" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="T65" s="2">
         <v>0.70917592592592593</v>
       </c>
       <c r="U65" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="V65">
         <v>353.57</v>
@@ -9317,13 +9317,13 @@
       <c r="G66" s="5"/>
       <c r="P66" s="2"/>
       <c r="S66" s="5" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="T66" s="2">
         <v>0.71015972222222223</v>
       </c>
       <c r="U66" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="V66">
         <v>356.87</v>
@@ -9357,10 +9357,10 @@
         <v>143.80000000000001</v>
       </c>
       <c r="AG66" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH66" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI66" s="4">
         <v>1.53</v>
@@ -9389,13 +9389,13 @@
       <c r="G67" s="5"/>
       <c r="P67" s="2"/>
       <c r="S67" s="5" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="T67" s="2">
         <v>0.71144108796296301</v>
       </c>
       <c r="U67" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="V67">
         <v>358.35</v>
@@ -9461,13 +9461,13 @@
       <c r="G68" s="5"/>
       <c r="P68" s="2"/>
       <c r="S68" s="5" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="T68" s="2">
         <v>0.71191122685185182</v>
       </c>
       <c r="U68" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="V68">
         <v>0.13</v>
@@ -9501,10 +9501,10 @@
         <v>-279.10000000000002</v>
       </c>
       <c r="AG68" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH68" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI68" s="4">
         <v>1.38</v>
@@ -9533,13 +9533,13 @@
       <c r="G69" s="5"/>
       <c r="P69" s="2"/>
       <c r="S69" s="5" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="T69" s="2">
         <v>0.71539583333333334</v>
       </c>
       <c r="U69" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="V69">
         <v>357.62</v>
@@ -9605,13 +9605,13 @@
       <c r="G70" s="5"/>
       <c r="P70" s="2"/>
       <c r="S70" s="5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="T70" s="2">
         <v>0.71842881944444448</v>
       </c>
       <c r="U70" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="V70">
         <v>355.83</v>
@@ -9645,10 +9645,10 @@
         <v>-99.3</v>
       </c>
       <c r="AG70" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH70" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI70" s="4">
         <v>1.8</v>
@@ -9677,13 +9677,13 @@
       <c r="G71" s="5"/>
       <c r="P71" s="2"/>
       <c r="S71" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="T71" s="2">
         <v>0.7198761574074074</v>
       </c>
       <c r="U71" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="V71">
         <v>357.18</v>
@@ -9717,10 +9717,10 @@
         <v>79.900000000000006</v>
       </c>
       <c r="AG71" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH71" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI71" s="4">
         <v>1.65</v>
@@ -9749,13 +9749,13 @@
       <c r="G72" s="5"/>
       <c r="P72" s="2"/>
       <c r="S72" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="T72" s="2">
         <v>0.72022442129629627</v>
       </c>
       <c r="U72" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="V72">
         <v>68.34</v>
@@ -9821,13 +9821,13 @@
       <c r="G73" s="5"/>
       <c r="P73" s="2"/>
       <c r="S73" s="5" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="T73" s="2">
         <v>0.72082418981481478</v>
       </c>
       <c r="U73" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="V73">
         <v>0.97</v>
@@ -9893,13 +9893,13 @@
       <c r="G74" s="5"/>
       <c r="P74" s="2"/>
       <c r="S74" s="5" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="T74" s="2">
         <v>0.72165810185185186</v>
       </c>
       <c r="U74" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="V74">
         <v>5.54</v>
@@ -9933,10 +9933,10 @@
         <v>239.8</v>
       </c>
       <c r="AG74" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH74" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI74" s="4">
         <v>1.25</v>
@@ -9965,13 +9965,13 @@
       <c r="G75" s="5"/>
       <c r="P75" s="2"/>
       <c r="S75" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="T75" s="2">
         <v>0.72303333333333331</v>
       </c>
       <c r="U75" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="V75">
         <v>4.9000000000000004</v>
@@ -10037,13 +10037,13 @@
       <c r="G76" s="5"/>
       <c r="P76" s="2"/>
       <c r="S76" s="5" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="T76" s="2">
         <v>0.72470983796296295</v>
       </c>
       <c r="U76" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="V76">
         <v>6.72</v>
@@ -10077,10 +10077,10 @@
         <v>38</v>
       </c>
       <c r="AG76" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH76" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI76" s="4">
         <v>1.59</v>
@@ -10109,13 +10109,13 @@
       <c r="G77" s="5"/>
       <c r="P77" s="2"/>
       <c r="S77" s="5" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="T77" s="2">
         <v>0.72498368055555551</v>
       </c>
       <c r="U77" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="V77">
         <v>359.59</v>
@@ -10149,10 +10149,10 @@
         <v>-167.9</v>
       </c>
       <c r="AG77" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH77" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI77" s="4">
         <v>2.5</v>
@@ -10181,13 +10181,13 @@
       <c r="G78" s="5"/>
       <c r="P78" s="2"/>
       <c r="S78" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="T78" s="2">
         <v>0.72603136574074079</v>
       </c>
       <c r="U78" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="V78">
         <v>341.42</v>
@@ -10221,10 +10221,10 @@
         <v>-134.1</v>
       </c>
       <c r="AG78" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH78" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI78" s="4">
         <v>1.1000000000000001</v>
@@ -10253,13 +10253,13 @@
       <c r="G79" s="5"/>
       <c r="P79" s="2"/>
       <c r="S79" s="5" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="T79" s="2">
         <v>0.72718171296296297</v>
       </c>
       <c r="U79" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="V79">
         <v>16.54</v>
@@ -10293,10 +10293,10 @@
         <v>-127</v>
       </c>
       <c r="AG79" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH79" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI79" s="4">
         <v>1.55</v>
@@ -10308,13 +10308,13 @@
         <v>1.4</v>
       </c>
       <c r="AL79" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM79" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AN79" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AO79" s="4">
         <v>9.6</v>
@@ -10325,13 +10325,13 @@
       <c r="G80" s="5"/>
       <c r="P80" s="2"/>
       <c r="S80" s="5" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="T80" s="2">
         <v>0.72746643518518517</v>
       </c>
       <c r="U80" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="V80">
         <v>356.32</v>
@@ -10365,10 +10365,10 @@
         <v>116.9</v>
       </c>
       <c r="AG80" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH80" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI80" s="4">
         <v>2.5</v>
@@ -10397,13 +10397,13 @@
       <c r="G81" s="5"/>
       <c r="P81" s="2"/>
       <c r="S81" s="5" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="T81" s="2">
         <v>0.72759537037037036</v>
       </c>
       <c r="U81" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="V81">
         <v>18.41</v>
@@ -10469,13 +10469,13 @@
       <c r="G82" s="5"/>
       <c r="P82" s="2"/>
       <c r="S82" s="5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="T82" s="2">
         <v>0.72961805555555559</v>
       </c>
       <c r="U82" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="V82">
         <v>356.02</v>
@@ -10509,10 +10509,10 @@
         <v>-42.3</v>
       </c>
       <c r="AG82" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH82" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI82" s="4">
         <v>0.9</v>
@@ -10524,13 +10524,13 @@
         <v>1.85</v>
       </c>
       <c r="AL82" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM82" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AN82" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AO82" s="4">
         <v>8.6999999999999993</v>
@@ -10541,13 +10541,13 @@
       <c r="G83" s="5"/>
       <c r="P83" s="2"/>
       <c r="S83" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="T83" s="2">
         <v>0.72992129629629632</v>
       </c>
       <c r="U83" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="V83">
         <v>357.44</v>
@@ -10581,10 +10581,10 @@
         <v>54</v>
       </c>
       <c r="AG83" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH83" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI83" s="4">
         <v>2.5</v>
@@ -10613,13 +10613,13 @@
       <c r="G84" s="5"/>
       <c r="P84" s="2"/>
       <c r="S84" s="5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="T84" s="2">
         <v>0.73049756944444444</v>
       </c>
       <c r="U84" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="V84">
         <v>325.55</v>
@@ -10685,13 +10685,13 @@
       <c r="G85" s="5"/>
       <c r="P85" s="2"/>
       <c r="S85" s="5" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="T85" s="2">
         <v>0.7315335648148148</v>
       </c>
       <c r="U85" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="V85">
         <v>354.84</v>
@@ -10725,10 +10725,10 @@
         <v>59.2</v>
       </c>
       <c r="AG85" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH85" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI85" s="4">
         <v>2.2999999999999998</v>
@@ -10737,7 +10737,7 @@
         <v>0.06</v>
       </c>
       <c r="AK85" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AL85" s="4">
         <v>24</v>
@@ -10757,13 +10757,13 @@
       <c r="G86" s="5"/>
       <c r="P86" s="2"/>
       <c r="S86" s="5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="T86" s="2">
         <v>0.73226851851851849</v>
       </c>
       <c r="U86" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="V86">
         <v>350.18</v>
@@ -10797,10 +10797,10 @@
         <v>2.1</v>
       </c>
       <c r="AG86" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH86" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI86" s="4">
         <v>1.55</v>
@@ -10829,13 +10829,13 @@
       <c r="G87" s="5"/>
       <c r="P87" s="2"/>
       <c r="S87" s="5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="T87" s="2">
         <v>0.73319212962962965</v>
       </c>
       <c r="U87" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="V87">
         <v>357.57</v>
@@ -10869,10 +10869,10 @@
         <v>122</v>
       </c>
       <c r="AG87" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH87" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI87" s="4">
         <v>2.5</v>
@@ -10901,13 +10901,13 @@
       <c r="G88" s="5"/>
       <c r="P88" s="2"/>
       <c r="S88" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="T88" s="2">
         <v>0.73345486111111113</v>
       </c>
       <c r="U88" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="V88">
         <v>350.8</v>
@@ -10941,10 +10941,10 @@
         <v>-178.6</v>
       </c>
       <c r="AG88" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH88" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI88" s="4">
         <v>1.3</v>
@@ -10973,13 +10973,13 @@
       <c r="G89" s="5"/>
       <c r="P89" s="2"/>
       <c r="S89" s="5" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="T89" s="2">
         <v>0.73353275462962964</v>
       </c>
       <c r="U89" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="V89">
         <v>345.56</v>
@@ -11045,13 +11045,13 @@
       <c r="G90" s="5"/>
       <c r="P90" s="2"/>
       <c r="S90" s="5" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="T90" s="2">
         <v>0.73444560185185181</v>
       </c>
       <c r="U90" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="V90">
         <v>21.32</v>
@@ -11085,10 +11085,10 @@
         <v>-52.1</v>
       </c>
       <c r="AG90" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH90" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI90" s="4">
         <v>0.99</v>
@@ -11117,13 +11117,13 @@
       <c r="G91" s="5"/>
       <c r="P91" s="2"/>
       <c r="S91" s="5" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="T91" s="2">
         <v>0.73514583333333328</v>
       </c>
       <c r="U91" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="V91">
         <v>3.45</v>
@@ -11157,10 +11157,10 @@
         <v>-55.3</v>
       </c>
       <c r="AG91" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH91" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI91" s="4">
         <v>1.69</v>
@@ -11189,13 +11189,13 @@
       <c r="G92" s="5"/>
       <c r="P92" s="2"/>
       <c r="S92" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="T92" s="2">
         <v>0.73659826388888883</v>
       </c>
       <c r="U92" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="V92">
         <v>338.17</v>
@@ -11261,13 +11261,13 @@
       <c r="G93" s="5"/>
       <c r="P93" s="2"/>
       <c r="S93" s="5" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="T93" s="2">
         <v>0.73868287037037028</v>
       </c>
       <c r="U93" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="V93">
         <v>2.1</v>
@@ -11301,10 +11301,10 @@
         <v>190.2</v>
       </c>
       <c r="AG93" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH93" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI93" s="4">
         <v>1.1000000000000001</v>
@@ -11333,13 +11333,13 @@
       <c r="G94" s="5"/>
       <c r="P94" s="2"/>
       <c r="S94" s="5" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="T94" s="2">
         <v>0.73952141203703703</v>
       </c>
       <c r="U94" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="V94">
         <v>28.09</v>
@@ -11373,10 +11373,10 @@
         <v>-146.9</v>
       </c>
       <c r="AG94" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH94" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI94" s="4">
         <v>1.7</v>
@@ -11405,13 +11405,13 @@
       <c r="G95" s="5"/>
       <c r="P95" s="2"/>
       <c r="S95" s="5" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="T95" s="2">
         <v>0.74129976851851853</v>
       </c>
       <c r="U95" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="V95">
         <v>356.69</v>
@@ -11445,10 +11445,10 @@
         <v>-355</v>
       </c>
       <c r="AG95" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH95" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI95" s="4">
         <v>1.5</v>
@@ -11477,13 +11477,13 @@
       <c r="G96" s="5"/>
       <c r="P96" s="2"/>
       <c r="S96" s="5" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="T96" s="2">
         <v>0.74172222222222228</v>
       </c>
       <c r="U96" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="V96">
         <v>3.84</v>
@@ -11517,10 +11517,10 @@
         <v>-83.5</v>
       </c>
       <c r="AG96" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH96" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI96" s="4">
         <v>1.62</v>
@@ -11549,13 +11549,13 @@
       <c r="G97" s="5"/>
       <c r="P97" s="2"/>
       <c r="S97" s="5" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="T97" s="2">
         <v>0.74227662037037034</v>
       </c>
       <c r="U97" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="V97">
         <v>7.73</v>
@@ -11589,10 +11589,10 @@
         <v>-65.900000000000006</v>
       </c>
       <c r="AG97" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH97" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI97" s="4">
         <v>1.62</v>
@@ -11621,13 +11621,13 @@
       <c r="G98" s="5"/>
       <c r="P98" s="2"/>
       <c r="S98" s="5" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="T98" s="2">
         <v>0.74320671296296292</v>
       </c>
       <c r="U98" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="V98">
         <v>353.53</v>
@@ -11693,13 +11693,13 @@
       <c r="G99" s="5"/>
       <c r="P99" s="2"/>
       <c r="S99" s="5" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="T99" s="2">
         <v>0.74359236111111104</v>
       </c>
       <c r="U99" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="V99">
         <v>358.57</v>
@@ -11733,10 +11733,10 @@
         <v>133.9</v>
       </c>
       <c r="AG99" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH99" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI99" s="4">
         <v>2.5</v>
@@ -11765,13 +11765,13 @@
       <c r="G100" s="5"/>
       <c r="P100" s="2"/>
       <c r="S100" s="5" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="T100" s="2">
         <v>0.74365393518518519</v>
       </c>
       <c r="U100" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="V100">
         <v>355.72</v>
@@ -11805,10 +11805,10 @@
         <v>-76.7</v>
       </c>
       <c r="AG100" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH100" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI100" s="4">
         <v>2.5</v>
@@ -11837,13 +11837,13 @@
       <c r="G101" s="5"/>
       <c r="P101" s="2"/>
       <c r="S101" s="5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="T101" s="2">
         <v>0.74614814814814812</v>
       </c>
       <c r="U101" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="V101">
         <v>5.13</v>
@@ -11877,10 +11877,10 @@
         <v>66.7</v>
       </c>
       <c r="AG101" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH101" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI101" s="4">
         <v>2.1</v>
@@ -11889,7 +11889,7 @@
         <v>0.15</v>
       </c>
       <c r="AK101" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AL101" s="4">
         <v>25.52</v>
@@ -11909,13 +11909,13 @@
       <c r="G102" s="5"/>
       <c r="P102" s="2"/>
       <c r="S102" s="5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="T102" s="2">
         <v>0.7493481481481481</v>
       </c>
       <c r="U102" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="V102">
         <v>348.03</v>
@@ -11949,10 +11949,10 @@
         <v>-108.4</v>
       </c>
       <c r="AG102" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH102" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI102" s="4">
         <v>0.7</v>
@@ -11981,13 +11981,13 @@
       <c r="G103" s="5"/>
       <c r="P103" s="2"/>
       <c r="S103" s="5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="T103" s="2">
         <v>0.75114351851851857</v>
       </c>
       <c r="U103" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="V103">
         <v>3.61</v>
@@ -12021,10 +12021,10 @@
         <v>68.099999999999994</v>
       </c>
       <c r="AG103" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH103" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI103" s="4">
         <v>2.5</v>
@@ -12053,13 +12053,13 @@
       <c r="G104" s="5"/>
       <c r="P104" s="2"/>
       <c r="S104" s="5" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="T104" s="2">
         <v>0.75126273148148148</v>
       </c>
       <c r="U104" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="V104">
         <v>2.77</v>
@@ -12084,19 +12084,19 @@
       </c>
       <c r="AC104" s="4"/>
       <c r="AD104" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AE104" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF104" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG104" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH104" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI104" s="4">
         <v>1.5</v>
@@ -12125,13 +12125,13 @@
       <c r="G105" s="5"/>
       <c r="P105" s="2"/>
       <c r="S105" s="5" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="T105" s="2">
         <v>0.75127916666666661</v>
       </c>
       <c r="U105" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="V105">
         <v>19.23</v>
@@ -12165,10 +12165,10 @@
         <v>-26.5</v>
       </c>
       <c r="AG105" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH105" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI105" s="4">
         <v>1.82</v>
@@ -12197,13 +12197,13 @@
       <c r="G106" s="5"/>
       <c r="P106" s="2"/>
       <c r="S106" s="5" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="T106" s="2">
         <v>0.75250462962962961</v>
       </c>
       <c r="U106" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="V106">
         <v>4.49</v>
@@ -12228,19 +12228,19 @@
       </c>
       <c r="AC106" s="4"/>
       <c r="AD106" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AE106" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF106" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG106" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH106" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI106" s="4">
         <v>0.75</v>
@@ -12269,13 +12269,13 @@
       <c r="G107" s="5"/>
       <c r="P107" s="2"/>
       <c r="S107" s="5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="T107" s="2">
         <v>0.7524770833333333</v>
       </c>
       <c r="U107" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="V107">
         <v>1.02</v>
@@ -12341,13 +12341,13 @@
       <c r="G108" s="5"/>
       <c r="P108" s="2"/>
       <c r="S108" s="5" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="T108" s="2">
         <v>0.75266793981481483</v>
       </c>
       <c r="U108" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="V108">
         <v>27.18</v>
@@ -12413,13 +12413,13 @@
       <c r="G109" s="5"/>
       <c r="P109" s="2"/>
       <c r="S109" s="5" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="T109" s="2">
         <v>0.75335231481481479</v>
       </c>
       <c r="U109" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="V109">
         <v>1.1399999999999999</v>
@@ -12453,10 +12453,10 @@
         <v>214.9</v>
       </c>
       <c r="AG109" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH109" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI109" s="4">
         <v>1.5</v>
@@ -12485,13 +12485,13 @@
       <c r="G110" s="5"/>
       <c r="P110" s="2"/>
       <c r="S110" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="T110" s="2">
         <v>0.75335277777777776</v>
       </c>
       <c r="U110" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="V110">
         <v>20.8</v>
@@ -12525,10 +12525,10 @@
         <v>44.4</v>
       </c>
       <c r="AG110" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH110" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI110" s="4">
         <v>1.74</v>
@@ -12557,13 +12557,13 @@
       <c r="G111" s="5"/>
       <c r="P111" s="2"/>
       <c r="S111" s="5" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="T111" s="2">
         <v>0.75426620370370367</v>
       </c>
       <c r="U111" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="V111">
         <v>3.29</v>
@@ -12597,10 +12597,10 @@
         <v>-8.8000000000000007</v>
       </c>
       <c r="AG111" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH111" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI111" s="4">
         <v>2.5</v>
@@ -12609,7 +12609,7 @@
         <v>0.03</v>
       </c>
       <c r="AK111" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AL111" s="4">
         <v>16.399999999999999</v>
@@ -12629,13 +12629,13 @@
       <c r="G112" s="5"/>
       <c r="P112" s="2"/>
       <c r="S112" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="T112" s="2">
         <v>0.7550993055555556</v>
       </c>
       <c r="U112" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="V112">
         <v>5.84</v>
@@ -12669,10 +12669,10 @@
         <v>-17.7</v>
       </c>
       <c r="AG112" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH112" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI112" s="4">
         <v>1.63</v>
@@ -12701,13 +12701,13 @@
       <c r="G113" s="5"/>
       <c r="P113" s="2"/>
       <c r="S113" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="T113" s="2">
         <v>0.75558287037037042</v>
       </c>
       <c r="U113" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="V113">
         <v>349.29</v>
@@ -12773,13 +12773,13 @@
       <c r="G114" s="5"/>
       <c r="P114" s="2"/>
       <c r="S114" s="5" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="T114" s="2">
         <v>0.75580798611111111</v>
       </c>
       <c r="U114" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="V114">
         <v>10.48</v>
@@ -12804,19 +12804,19 @@
       </c>
       <c r="AC114" s="4"/>
       <c r="AD114" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AE114" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF114" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG114" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH114" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI114" s="4">
         <v>0.85</v>
@@ -12828,13 +12828,13 @@
         <v>1.65</v>
       </c>
       <c r="AL114" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM114" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AN114" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AO114" s="4">
         <v>8.43</v>
@@ -12845,13 +12845,13 @@
       <c r="G115" s="5"/>
       <c r="P115" s="2"/>
       <c r="S115" s="5" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="T115" s="2">
         <v>0.75631944444444443</v>
       </c>
       <c r="U115" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="V115">
         <v>346.9</v>
@@ -12876,19 +12876,19 @@
       </c>
       <c r="AC115" s="4"/>
       <c r="AD115" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AE115" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF115" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG115" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH115" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI115" s="4">
         <v>0.9</v>
@@ -12900,13 +12900,13 @@
         <v>1.05</v>
       </c>
       <c r="AL115" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM115" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AN115" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AO115" s="4">
         <v>9.1</v>
@@ -12917,13 +12917,13 @@
       <c r="G116" s="5"/>
       <c r="P116" s="2"/>
       <c r="S116" s="5" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="T116" s="2">
         <v>0.75645370370370368</v>
       </c>
       <c r="U116" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="V116">
         <v>5.26</v>
@@ -12957,10 +12957,10 @@
         <v>6.1</v>
       </c>
       <c r="AG116" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH116" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI116" s="4">
         <v>1.1599999999999999</v>
@@ -12989,13 +12989,13 @@
       <c r="G117" s="5"/>
       <c r="P117" s="2"/>
       <c r="S117" s="5" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="T117" s="2">
         <v>0.75667245370370373</v>
       </c>
       <c r="U117" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="V117">
         <v>9.7899999999999991</v>
@@ -13029,10 +13029,10 @@
         <v>-227.4</v>
       </c>
       <c r="AG117" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH117" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI117" s="4">
         <v>0.95</v>
@@ -13044,13 +13044,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="AL117" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM117" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AN117" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AO117" s="4">
         <v>7.72</v>
@@ -13061,13 +13061,13 @@
       <c r="G118" s="5"/>
       <c r="P118" s="2"/>
       <c r="S118" s="5" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="T118" s="2">
         <v>0.75714814814814813</v>
       </c>
       <c r="U118" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="V118">
         <v>0.2</v>
@@ -13133,13 +13133,13 @@
       <c r="G119" s="5"/>
       <c r="P119" s="2"/>
       <c r="S119" s="5" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="T119" s="2">
         <v>0.75745601851851851</v>
       </c>
       <c r="U119" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="V119">
         <v>21.83</v>
@@ -13173,10 +13173,10 @@
         <v>169.2</v>
       </c>
       <c r="AG119" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH119" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI119" s="4">
         <v>1.33</v>
@@ -13205,13 +13205,13 @@
       <c r="G120" s="5"/>
       <c r="P120" s="2"/>
       <c r="S120" s="5" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="T120" s="2">
         <v>0.75851620370370376</v>
       </c>
       <c r="U120" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="V120">
         <v>8.3699999999999992</v>
@@ -13245,10 +13245,10 @@
         <v>104.2</v>
       </c>
       <c r="AG120" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH120" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI120" s="4">
         <v>0.56999999999999995</v>
@@ -13277,13 +13277,13 @@
       <c r="G121" s="5"/>
       <c r="P121" s="2"/>
       <c r="S121" s="5" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="T121" s="2">
         <v>0.75947685185185188</v>
       </c>
       <c r="U121" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="V121">
         <v>0.48</v>
@@ -13317,10 +13317,10 @@
         <v>-20.3</v>
       </c>
       <c r="AG121" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH121" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI121" s="4">
         <v>1.31</v>
@@ -13349,13 +13349,13 @@
       <c r="G122" s="5"/>
       <c r="P122" s="2"/>
       <c r="S122" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="T122" s="2">
         <v>0.75979861111111113</v>
       </c>
       <c r="U122" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="V122">
         <v>3.36</v>
@@ -13380,19 +13380,19 @@
       </c>
       <c r="AC122" s="4"/>
       <c r="AD122" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AE122" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF122" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG122" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH122" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI122" s="4">
         <v>1</v>
@@ -13404,13 +13404,13 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="AL122" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM122" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AN122" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AO122" s="4">
         <v>7.8</v>
@@ -13421,13 +13421,13 @@
       <c r="G123" s="5"/>
       <c r="P123" s="2"/>
       <c r="S123" s="5" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="T123" s="2">
         <v>0.76285300925925925</v>
       </c>
       <c r="U123" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="V123">
         <v>14.14</v>
@@ -13452,19 +13452,19 @@
       </c>
       <c r="AC123" s="4"/>
       <c r="AD123" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AE123" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF123" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG123" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH123" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI123" s="4">
         <v>1.33</v>
@@ -13473,19 +13473,19 @@
         <v>0.7</v>
       </c>
       <c r="AK123" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AL123" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM123" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AN123" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AO123" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="124" spans="1:41" x14ac:dyDescent="0.2">
@@ -13493,13 +13493,13 @@
       <c r="G124" s="5"/>
       <c r="P124" s="2"/>
       <c r="S124" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="T124" s="2">
         <v>0.76293518518518522</v>
       </c>
       <c r="U124" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="V124">
         <v>342.14</v>
@@ -13533,10 +13533,10 @@
         <v>224.9</v>
       </c>
       <c r="AG124" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH124" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI124" s="4">
         <v>1.47</v>
@@ -13565,13 +13565,13 @@
       <c r="G125" s="5"/>
       <c r="P125" s="2"/>
       <c r="S125" s="5" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="T125" s="2">
         <v>0.76644108796296295</v>
       </c>
       <c r="U125" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="V125">
         <v>2.79</v>
@@ -13637,13 +13637,13 @@
       <c r="G126" s="5"/>
       <c r="P126" s="2"/>
       <c r="S126" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="T126" s="2">
         <v>0.76704641203703705</v>
       </c>
       <c r="U126" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="V126">
         <v>7.8</v>
@@ -13709,13 +13709,13 @@
       <c r="G127" s="5"/>
       <c r="P127" s="2"/>
       <c r="S127" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="T127" s="2">
         <v>0.77148263888888891</v>
       </c>
       <c r="U127" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="V127">
         <v>7.9</v>
@@ -13749,10 +13749,10 @@
         <v>27.5</v>
       </c>
       <c r="AG127" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH127" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI127" s="4">
         <v>1.33</v>
@@ -13781,13 +13781,13 @@
       <c r="G128" s="5"/>
       <c r="P128" s="2"/>
       <c r="S128" s="5" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="T128" s="2">
         <v>0.77179513888888895</v>
       </c>
       <c r="U128" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V128">
         <v>1.72</v>
@@ -13821,10 +13821,10 @@
         <v>47.5</v>
       </c>
       <c r="AG128" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH128" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI128" s="4">
         <v>1.38</v>
@@ -13853,13 +13853,13 @@
       <c r="G129" s="5"/>
       <c r="P129" s="2"/>
       <c r="S129" s="5" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="T129" s="2">
         <v>0.77215393518518527</v>
       </c>
       <c r="U129" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="V129">
         <v>9.81</v>
@@ -13893,10 +13893,10 @@
         <v>-47.3</v>
       </c>
       <c r="AG129" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH129" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI129" s="4">
         <v>1.99</v>
@@ -13925,13 +13925,13 @@
       <c r="G130" s="5"/>
       <c r="P130" s="2"/>
       <c r="S130" s="5" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="T130" s="2">
         <v>0.77483368055555557</v>
       </c>
       <c r="U130" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="V130">
         <v>1.53</v>
@@ -13965,10 +13965,10 @@
         <v>-104.3</v>
       </c>
       <c r="AG130" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH130" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI130" s="4">
         <v>1.8</v>
@@ -13997,13 +13997,13 @@
       <c r="G131" s="5"/>
       <c r="P131" s="2"/>
       <c r="S131" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="T131" s="2">
         <v>0.77527708333333334</v>
       </c>
       <c r="U131" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="V131">
         <v>9.89</v>
@@ -14069,13 +14069,13 @@
       <c r="G132" s="5"/>
       <c r="P132" s="2"/>
       <c r="S132" s="5" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="T132" s="2">
         <v>0.77881828703703693</v>
       </c>
       <c r="U132" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="V132">
         <v>14.11</v>
@@ -14109,10 +14109,10 @@
         <v>-32.299999999999997</v>
       </c>
       <c r="AG132" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH132" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI132" s="4">
         <v>1.53</v>
@@ -14141,13 +14141,13 @@
       <c r="G133" s="5"/>
       <c r="P133" s="2"/>
       <c r="S133" s="5" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="T133" s="2">
         <v>0.78000879629629627</v>
       </c>
       <c r="U133" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="V133">
         <v>2.85</v>
@@ -14213,13 +14213,13 @@
       <c r="G134" s="5"/>
       <c r="P134" s="2"/>
       <c r="S134" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="T134" s="2">
         <v>0.78390856481481475</v>
       </c>
       <c r="U134" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="V134">
         <v>31.31</v>
@@ -14244,19 +14244,19 @@
       </c>
       <c r="AC134" s="4"/>
       <c r="AD134" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AE134" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF134" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG134" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH134" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI134" s="4">
         <v>1.37</v>
@@ -14268,13 +14268,13 @@
         <v>0.65</v>
       </c>
       <c r="AL134" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM134" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AN134" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AO134" s="4">
         <v>7.89</v>
@@ -14285,13 +14285,13 @@
       <c r="G135" s="5"/>
       <c r="P135" s="2"/>
       <c r="S135" s="5" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="T135" s="2">
         <v>0.7868553240740741</v>
       </c>
       <c r="U135" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="V135">
         <v>25.35</v>
@@ -14357,13 +14357,13 @@
       <c r="G136" s="5"/>
       <c r="P136" s="2"/>
       <c r="S136" s="5" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="T136" s="2">
         <v>0.78823298611111114</v>
       </c>
       <c r="U136" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="V136">
         <v>5.61</v>
@@ -14429,13 +14429,13 @@
       <c r="G137" s="5"/>
       <c r="P137" s="2"/>
       <c r="S137" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="T137" s="2">
         <v>0.78826435185185173</v>
       </c>
       <c r="U137" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="V137">
         <v>12.88</v>
@@ -14469,10 +14469,10 @@
         <v>32.700000000000003</v>
       </c>
       <c r="AG137" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH137" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI137" s="4">
         <v>2.0699999999999998</v>
@@ -14501,13 +14501,13 @@
       <c r="G138" s="5"/>
       <c r="P138" s="2"/>
       <c r="S138" s="5" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="T138" s="2">
         <v>0.79135590277777768</v>
       </c>
       <c r="U138" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="V138">
         <v>7.0000000000000007E-2</v>
@@ -14541,10 +14541,10 @@
         <v>-88.3</v>
       </c>
       <c r="AG138" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH138" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI138" s="4">
         <v>1.1100000000000001</v>
@@ -14573,13 +14573,13 @@
       <c r="G139" s="5"/>
       <c r="P139" s="2"/>
       <c r="S139" s="5" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="T139" s="2">
         <v>0.79531597222222228</v>
       </c>
       <c r="U139" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="V139">
         <v>36.200000000000003</v>
@@ -14613,10 +14613,10 @@
         <v>-47.2</v>
       </c>
       <c r="AG139" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH139" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI139" s="4">
         <v>0.79</v>
@@ -14645,13 +14645,13 @@
       <c r="G140" s="5"/>
       <c r="P140" s="2"/>
       <c r="S140" s="5" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="T140" s="2">
         <v>0.79921423611111109</v>
       </c>
       <c r="U140" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="V140">
         <v>336.49</v>
@@ -14717,13 +14717,13 @@
       <c r="G141" s="5"/>
       <c r="P141" s="2"/>
       <c r="S141" s="5" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="T141" s="2">
         <v>0.79944456018518517</v>
       </c>
       <c r="U141" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="V141">
         <v>36.11</v>
@@ -14757,10 +14757,10 @@
         <v>-13.2</v>
       </c>
       <c r="AG141" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH141" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI141" s="4">
         <v>1.65</v>
@@ -14789,13 +14789,13 @@
       <c r="G142" s="5"/>
       <c r="P142" s="2"/>
       <c r="S142" s="5" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="T142" s="2">
         <v>0.80318946759259269</v>
       </c>
       <c r="U142" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="V142">
         <v>62.66</v>
@@ -14861,13 +14861,13 @@
       <c r="G143" s="5"/>
       <c r="P143" s="2"/>
       <c r="S143" s="5" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="T143" s="2">
         <v>0.80398055555555559</v>
       </c>
       <c r="U143" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="V143">
         <v>3.39</v>
@@ -14901,10 +14901,10 @@
         <v>172.5</v>
       </c>
       <c r="AG143" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH143" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI143" s="4">
         <v>0.93</v>
@@ -14933,13 +14933,13 @@
       <c r="G144" s="5"/>
       <c r="P144" s="2"/>
       <c r="S144" s="5" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="T144" s="2">
         <v>0.80419097222222224</v>
       </c>
       <c r="U144" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="V144">
         <v>52.43</v>
@@ -14973,10 +14973,10 @@
         <v>-15.6</v>
       </c>
       <c r="AG144" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH144" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI144" s="4">
         <v>0.57999999999999996</v>
@@ -15005,13 +15005,13 @@
       <c r="G145" s="5"/>
       <c r="P145" s="2"/>
       <c r="S145" s="5" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="T145" s="2">
         <v>0.81162164351851851</v>
       </c>
       <c r="U145" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="V145">
         <v>8.5500000000000007</v>
@@ -15045,10 +15045,10 @@
         <v>122.4</v>
       </c>
       <c r="AG145" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH145" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI145" s="4">
         <v>0.88</v>
@@ -15077,13 +15077,13 @@
       <c r="G146" s="5"/>
       <c r="P146" s="2"/>
       <c r="S146" s="5" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="T146" s="2">
         <v>0.819441087962963</v>
       </c>
       <c r="U146" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="V146">
         <v>8.7899999999999991</v>
@@ -15149,13 +15149,13 @@
       <c r="G147" s="5"/>
       <c r="P147" s="2"/>
       <c r="S147" s="5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T147" s="2">
         <v>0.82065289351851856</v>
       </c>
       <c r="U147" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="V147">
         <v>5.76</v>
@@ -15189,10 +15189,10 @@
         <v>136.19999999999999</v>
       </c>
       <c r="AG147" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH147" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI147" s="4">
         <v>0.6</v>
@@ -15221,13 +15221,13 @@
       <c r="G148" s="5"/>
       <c r="P148" s="2"/>
       <c r="S148" s="5" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="T148" s="2">
         <v>0.82308333333333328</v>
       </c>
       <c r="U148" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="V148">
         <v>31.81</v>
@@ -15261,10 +15261,10 @@
         <v>-56</v>
       </c>
       <c r="AG148" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH148" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI148" s="4">
         <v>0.56999999999999995</v>
@@ -15293,13 +15293,13 @@
       <c r="G149" s="5"/>
       <c r="P149" s="2"/>
       <c r="S149" s="5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="T149" s="2">
         <v>0.82901030092592598</v>
       </c>
       <c r="U149" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="V149">
         <v>56.75</v>
@@ -15365,13 +15365,13 @@
       <c r="G150" s="5"/>
       <c r="P150" s="2"/>
       <c r="S150" s="5" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="T150" s="2">
         <v>0.83755428240740748</v>
       </c>
       <c r="U150" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="V150">
         <v>20.3</v>
@@ -15437,13 +15437,13 @@
       <c r="G151" s="5"/>
       <c r="P151" s="2"/>
       <c r="S151" s="5" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="T151" s="2">
         <v>0.85707604166666662</v>
       </c>
       <c r="U151" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="V151">
         <v>52.1</v>
@@ -15509,13 +15509,13 @@
       <c r="G152" s="5"/>
       <c r="P152" s="2"/>
       <c r="S152" s="5" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="T152" s="2">
         <v>0.87045949074074069</v>
       </c>
       <c r="U152" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="V152">
         <v>35.159999999999997</v>
@@ -15549,10 +15549,10 @@
         <v>-336.2</v>
       </c>
       <c r="AG152" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH152" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI152" s="4">
         <v>1.21</v>
@@ -15581,13 +15581,13 @@
       <c r="G153" s="5"/>
       <c r="P153" s="2"/>
       <c r="S153" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="T153" s="2">
         <v>0.8760344907407408</v>
       </c>
       <c r="U153" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="V153">
         <v>63.77</v>
@@ -15621,10 +15621,10 @@
         <v>-371.3</v>
       </c>
       <c r="AG153" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH153" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI153" s="4">
         <v>1.41</v>
@@ -15653,13 +15653,13 @@
       <c r="G154" s="5"/>
       <c r="P154" s="2"/>
       <c r="S154" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="T154" s="2">
         <v>0.89581400462962968</v>
       </c>
       <c r="U154" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="V154">
         <v>65.010000000000005</v>
@@ -15725,13 +15725,13 @@
       <c r="G155" s="5"/>
       <c r="P155" s="2"/>
       <c r="S155" s="5" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="T155" s="2">
         <v>0.89822939814814817</v>
       </c>
       <c r="U155" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="V155">
         <v>53.37</v>
@@ -15797,13 +15797,13 @@
       <c r="G156" s="5"/>
       <c r="P156" s="2"/>
       <c r="S156" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="T156" s="2">
         <v>0.90303379629629621</v>
       </c>
       <c r="U156" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="V156">
         <v>27.18</v>
@@ -15869,13 +15869,13 @@
       <c r="G157" s="5"/>
       <c r="P157" s="2"/>
       <c r="S157" s="5" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="T157" s="2">
         <v>0.90739398148148143</v>
       </c>
       <c r="U157" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="V157">
         <v>30.51</v>
@@ -15909,10 +15909,10 @@
         <v>32.5</v>
       </c>
       <c r="AG157" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH157" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI157" s="4">
         <v>2.98</v>
@@ -15941,13 +15941,13 @@
       <c r="G158" s="5"/>
       <c r="P158" s="2"/>
       <c r="S158" s="5" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="T158" s="2">
         <v>0.96301435185185191</v>
       </c>
       <c r="U158" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="V158">
         <v>87.1</v>
@@ -16013,13 +16013,13 @@
       <c r="G159" s="5"/>
       <c r="P159" s="2"/>
       <c r="S159" s="5" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="T159" s="2">
         <v>0.96419710648148149</v>
       </c>
       <c r="U159" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="V159">
         <v>53.39</v>
